--- a/docs/persistence.xlsx
+++ b/docs/persistence.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\casadje\GitHub\EFAS_skill\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D21AB28-3AE5-4F55-BD04-B564BB1C1F2D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE5052E-F06C-4523-84B5-EAE3F85C59CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9780" activeTab="2" xr2:uid="{8AF23766-066E-4445-BF6B-1330C2CD65A9}"/>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14610" activeTab="3" xr2:uid="{4D6A3DC2-48CE-4230-B68E-8C1EDE6084AC}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14610" activeTab="3" xr2:uid="{4D6A3DC2-48CE-4230-B68E-8C1EDE6084AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8591,16 +8591,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3DDED38-1AEC-47FD-A4DD-1A3DC79B2BCA}">
-  <dimension ref="A1:AE42"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="31" width="2.7109375" customWidth="1"/>
+    <col min="4" max="33" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D1" s="15" t="s">
         <v>0</v>
       </c>
@@ -8631,94 +8631,98 @@
       <c r="AC1" s="15"/>
       <c r="AD1" s="15"/>
       <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
     </row>
-    <row r="2" spans="1:31" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="47.25" x14ac:dyDescent="0.25">
       <c r="D2" s="12">
         <v>44927</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12">
         <v>44927.5</v>
       </c>
-      <c r="F2" s="12">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12">
         <v>44928</v>
       </c>
-      <c r="G2" s="12">
+      <c r="I2" s="12">
         <v>44928.5</v>
       </c>
-      <c r="H2" s="12">
+      <c r="J2" s="12">
         <v>44929</v>
       </c>
-      <c r="I2" s="12">
+      <c r="K2" s="12">
         <v>44929.5</v>
       </c>
-      <c r="J2" s="12">
+      <c r="L2" s="12">
         <v>44930</v>
       </c>
-      <c r="K2" s="12">
+      <c r="M2" s="12">
         <v>44930.5</v>
       </c>
-      <c r="L2" s="12">
+      <c r="N2" s="12">
         <v>44931</v>
       </c>
-      <c r="M2" s="12">
+      <c r="O2" s="12">
         <v>44931.5</v>
       </c>
-      <c r="N2" s="12">
+      <c r="P2" s="12">
         <v>44932</v>
       </c>
-      <c r="O2" s="12">
+      <c r="Q2" s="12">
         <v>44932.5</v>
       </c>
-      <c r="P2" s="12">
+      <c r="R2" s="12">
         <v>44933</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="S2" s="12">
         <v>44933.5</v>
       </c>
-      <c r="R2" s="12">
+      <c r="T2" s="12">
         <v>44934</v>
       </c>
-      <c r="S2" s="12">
+      <c r="U2" s="12">
         <v>44934.5</v>
       </c>
-      <c r="T2" s="12">
+      <c r="V2" s="12">
         <v>44935</v>
       </c>
-      <c r="U2" s="12">
+      <c r="W2" s="12">
         <v>44935.5</v>
       </c>
-      <c r="V2" s="12">
+      <c r="X2" s="12">
         <v>44936</v>
       </c>
-      <c r="W2" s="12">
+      <c r="Y2" s="12">
         <v>44936.5</v>
       </c>
-      <c r="X2" s="12">
+      <c r="Z2" s="12">
         <v>44937</v>
       </c>
-      <c r="Y2" s="12">
+      <c r="AA2" s="12">
         <v>44937.5</v>
       </c>
-      <c r="Z2" s="12">
+      <c r="AB2" s="12">
         <v>44938</v>
       </c>
-      <c r="AA2" s="12">
+      <c r="AC2" s="12">
         <v>44938.5</v>
       </c>
-      <c r="AB2" s="12">
+      <c r="AD2" s="12">
         <v>44939</v>
       </c>
-      <c r="AC2" s="12">
+      <c r="AE2" s="12">
         <v>44939.5</v>
       </c>
-      <c r="AD2" s="12">
+      <c r="AF2" s="12">
         <v>44940</v>
       </c>
-      <c r="AE2" s="12">
+      <c r="AG2" s="12">
         <v>44940.5</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
@@ -8731,15 +8735,11 @@
       <c r="D3" s="13">
         <v>0</v>
       </c>
-      <c r="E3" s="13">
-        <v>0</v>
-      </c>
+      <c r="E3" s="13"/>
       <c r="F3" s="13">
         <v>0</v>
       </c>
-      <c r="G3" s="13">
-        <v>0</v>
-      </c>
+      <c r="G3" s="13"/>
       <c r="H3" s="13">
         <v>0</v>
       </c>
@@ -8812,8 +8812,14 @@
       <c r="AE3" s="13">
         <v>0</v>
       </c>
+      <c r="AF3" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="16"/>
       <c r="C4">
@@ -8822,15 +8828,11 @@
       <c r="D4" s="13">
         <v>0</v>
       </c>
-      <c r="E4" s="13">
-        <v>0</v>
-      </c>
+      <c r="E4" s="13"/>
       <c r="F4" s="13">
         <v>0</v>
       </c>
-      <c r="G4" s="13">
-        <v>0</v>
-      </c>
+      <c r="G4" s="13"/>
       <c r="H4" s="13">
         <v>0</v>
       </c>
@@ -8903,8 +8905,14 @@
       <c r="AE4" s="13">
         <v>0</v>
       </c>
+      <c r="AF4" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="14"/>
       <c r="B5" s="16"/>
       <c r="C5">
@@ -8913,15 +8921,11 @@
       <c r="D5" s="13">
         <v>0</v>
       </c>
-      <c r="E5" s="13">
-        <v>0</v>
-      </c>
+      <c r="E5" s="13"/>
       <c r="F5" s="13">
         <v>0</v>
       </c>
-      <c r="G5" s="13">
-        <v>0</v>
-      </c>
+      <c r="G5" s="13"/>
       <c r="H5" s="13">
         <v>0</v>
       </c>
@@ -8994,8 +8998,14 @@
       <c r="AE5" s="13">
         <v>0</v>
       </c>
+      <c r="AF5" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="16"/>
       <c r="C6">
@@ -9004,15 +9014,11 @@
       <c r="D6" s="13">
         <v>0</v>
       </c>
-      <c r="E6" s="13">
-        <v>0</v>
-      </c>
+      <c r="E6" s="13"/>
       <c r="F6" s="13">
         <v>0</v>
       </c>
-      <c r="G6" s="13">
-        <v>0</v>
-      </c>
+      <c r="G6" s="13"/>
       <c r="H6" s="13">
         <v>0</v>
       </c>
@@ -9085,8 +9091,14 @@
       <c r="AE6" s="13">
         <v>0</v>
       </c>
+      <c r="AF6" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="16">
         <v>2</v>
@@ -9097,15 +9109,11 @@
       <c r="D7" s="13">
         <v>0</v>
       </c>
-      <c r="E7" s="13">
-        <v>0</v>
-      </c>
+      <c r="E7" s="13"/>
       <c r="F7" s="13">
         <v>0</v>
       </c>
-      <c r="G7" s="13">
-        <v>0</v>
-      </c>
+      <c r="G7" s="13"/>
       <c r="H7" s="13">
         <v>0</v>
       </c>
@@ -9178,8 +9186,14 @@
       <c r="AE7" s="13">
         <v>0</v>
       </c>
+      <c r="AF7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="16"/>
       <c r="C8">
@@ -9188,15 +9202,11 @@
       <c r="D8" s="13">
         <v>0</v>
       </c>
-      <c r="E8" s="13">
-        <v>0</v>
-      </c>
+      <c r="E8" s="13"/>
       <c r="F8" s="13">
         <v>0</v>
       </c>
-      <c r="G8" s="13">
-        <v>0</v>
-      </c>
+      <c r="G8" s="13"/>
       <c r="H8" s="13">
         <v>0</v>
       </c>
@@ -9269,8 +9279,14 @@
       <c r="AE8" s="13">
         <v>0</v>
       </c>
+      <c r="AF8" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="16"/>
       <c r="C9">
@@ -9279,15 +9295,11 @@
       <c r="D9" s="13">
         <v>0</v>
       </c>
-      <c r="E9" s="13">
-        <v>0</v>
-      </c>
+      <c r="E9" s="13"/>
       <c r="F9" s="13">
         <v>0</v>
       </c>
-      <c r="G9" s="13">
-        <v>0</v>
-      </c>
+      <c r="G9" s="13"/>
       <c r="H9" s="13">
         <v>0</v>
       </c>
@@ -9360,8 +9372,14 @@
       <c r="AE9" s="13">
         <v>0</v>
       </c>
+      <c r="AF9" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="16"/>
       <c r="C10">
@@ -9370,15 +9388,11 @@
       <c r="D10" s="13">
         <v>0</v>
       </c>
-      <c r="E10" s="13">
-        <v>0</v>
-      </c>
+      <c r="E10" s="13"/>
       <c r="F10" s="13">
         <v>0</v>
       </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
+      <c r="G10" s="13"/>
       <c r="H10" s="13">
         <v>0</v>
       </c>
@@ -9451,8 +9465,14 @@
       <c r="AE10" s="13">
         <v>0</v>
       </c>
+      <c r="AF10" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="16">
         <v>3</v>
@@ -9463,15 +9483,11 @@
       <c r="D11" s="13">
         <v>0</v>
       </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
+      <c r="E11" s="13"/>
       <c r="F11" s="13">
         <v>0</v>
       </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
+      <c r="G11" s="13"/>
       <c r="H11" s="13">
         <v>0</v>
       </c>
@@ -9544,8 +9560,14 @@
       <c r="AE11" s="13">
         <v>0</v>
       </c>
+      <c r="AF11" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
       <c r="B12" s="16"/>
       <c r="C12">
@@ -9554,15 +9576,11 @@
       <c r="D12" s="13">
         <v>0</v>
       </c>
-      <c r="E12" s="13">
-        <v>0</v>
-      </c>
+      <c r="E12" s="13"/>
       <c r="F12" s="13">
         <v>0</v>
       </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
+      <c r="G12" s="13"/>
       <c r="H12" s="13">
         <v>0</v>
       </c>
@@ -9635,8 +9653,14 @@
       <c r="AE12" s="13">
         <v>0</v>
       </c>
+      <c r="AF12" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="16"/>
       <c r="C13">
@@ -9645,15 +9669,11 @@
       <c r="D13" s="13">
         <v>0</v>
       </c>
-      <c r="E13" s="13">
-        <v>0</v>
-      </c>
+      <c r="E13" s="13"/>
       <c r="F13" s="13">
         <v>0</v>
       </c>
-      <c r="G13" s="13">
-        <v>0</v>
-      </c>
+      <c r="G13" s="13"/>
       <c r="H13" s="13">
         <v>0</v>
       </c>
@@ -9726,8 +9746,14 @@
       <c r="AE13" s="13">
         <v>0</v>
       </c>
+      <c r="AF13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
       <c r="B14" s="16"/>
       <c r="C14">
@@ -9736,15 +9762,11 @@
       <c r="D14" s="13">
         <v>0</v>
       </c>
-      <c r="E14" s="13">
-        <v>0</v>
-      </c>
+      <c r="E14" s="13"/>
       <c r="F14" s="13">
         <v>0</v>
       </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
+      <c r="G14" s="13"/>
       <c r="H14" s="13">
         <v>0</v>
       </c>
@@ -9817,8 +9839,14 @@
       <c r="AE14" s="13">
         <v>0</v>
       </c>
+      <c r="AF14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="16">
         <v>4</v>
@@ -9829,15 +9857,11 @@
       <c r="D15" s="13">
         <v>0</v>
       </c>
-      <c r="E15" s="13">
-        <v>0</v>
-      </c>
+      <c r="E15" s="13"/>
       <c r="F15" s="13">
         <v>0</v>
       </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
+      <c r="G15" s="13"/>
       <c r="H15" s="13">
         <v>0</v>
       </c>
@@ -9910,8 +9934,14 @@
       <c r="AE15" s="13">
         <v>0</v>
       </c>
+      <c r="AF15" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="14"/>
       <c r="B16" s="16"/>
       <c r="C16">
@@ -9920,15 +9950,11 @@
       <c r="D16" s="13">
         <v>0</v>
       </c>
-      <c r="E16" s="13">
-        <v>0</v>
-      </c>
+      <c r="E16" s="13"/>
       <c r="F16" s="13">
         <v>0</v>
       </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
+      <c r="G16" s="13"/>
       <c r="H16" s="13">
         <v>0</v>
       </c>
@@ -10001,8 +10027,14 @@
       <c r="AE16" s="13">
         <v>0</v>
       </c>
+      <c r="AF16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="16"/>
       <c r="C17">
@@ -10011,15 +10043,11 @@
       <c r="D17" s="13">
         <v>0</v>
       </c>
-      <c r="E17" s="13">
-        <v>0</v>
-      </c>
+      <c r="E17" s="13"/>
       <c r="F17" s="13">
         <v>0</v>
       </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
+      <c r="G17" s="13"/>
       <c r="H17" s="13">
         <v>0</v>
       </c>
@@ -10092,8 +10120,14 @@
       <c r="AE17" s="13">
         <v>0</v>
       </c>
+      <c r="AF17" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="14"/>
       <c r="B18" s="16"/>
       <c r="C18">
@@ -10102,15 +10136,11 @@
       <c r="D18" s="13">
         <v>0</v>
       </c>
-      <c r="E18" s="13">
-        <v>0</v>
-      </c>
+      <c r="E18" s="13"/>
       <c r="F18" s="13">
         <v>0</v>
       </c>
-      <c r="G18" s="13">
-        <v>0</v>
-      </c>
+      <c r="G18" s="13"/>
       <c r="H18" s="13">
         <v>0</v>
       </c>
@@ -10183,8 +10213,14 @@
       <c r="AE18" s="13">
         <v>0</v>
       </c>
+      <c r="AF18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
       <c r="B19" s="16">
         <v>5</v>
@@ -10195,15 +10231,11 @@
       <c r="D19" s="13">
         <v>0</v>
       </c>
-      <c r="E19" s="13">
-        <v>0</v>
-      </c>
+      <c r="E19" s="13"/>
       <c r="F19" s="13">
         <v>0</v>
       </c>
-      <c r="G19" s="13">
-        <v>0</v>
-      </c>
+      <c r="G19" s="13"/>
       <c r="H19" s="13">
         <v>0</v>
       </c>
@@ -10276,8 +10308,14 @@
       <c r="AE19" s="13">
         <v>0</v>
       </c>
+      <c r="AF19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="16"/>
       <c r="C20">
@@ -10286,15 +10324,11 @@
       <c r="D20" s="13">
         <v>0</v>
       </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
+      <c r="E20" s="13"/>
       <c r="F20" s="13">
         <v>0</v>
       </c>
-      <c r="G20" s="13">
-        <v>0</v>
-      </c>
+      <c r="G20" s="13"/>
       <c r="H20" s="13">
         <v>0</v>
       </c>
@@ -10367,8 +10401,14 @@
       <c r="AE20" s="13">
         <v>0</v>
       </c>
+      <c r="AF20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="16"/>
       <c r="C21">
@@ -10377,15 +10417,11 @@
       <c r="D21" s="13">
         <v>0</v>
       </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
+      <c r="E21" s="13"/>
       <c r="F21" s="13">
         <v>0</v>
       </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
+      <c r="G21" s="13"/>
       <c r="H21" s="13">
         <v>0</v>
       </c>
@@ -10432,7 +10468,7 @@
         <v>0</v>
       </c>
       <c r="W21" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" s="13">
         <v>0</v>
@@ -10458,8 +10494,14 @@
       <c r="AE21" s="13">
         <v>0</v>
       </c>
+      <c r="AF21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="14"/>
       <c r="B22" s="16"/>
       <c r="C22">
@@ -10468,15 +10510,11 @@
       <c r="D22" s="13">
         <v>0</v>
       </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
+      <c r="E22" s="13"/>
       <c r="F22" s="13">
         <v>0</v>
       </c>
-      <c r="G22" s="13">
-        <v>0</v>
-      </c>
+      <c r="G22" s="13"/>
       <c r="H22" s="13">
         <v>0</v>
       </c>
@@ -10523,7 +10561,7 @@
         <v>0</v>
       </c>
       <c r="W22" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="13">
         <v>0</v>
@@ -10549,8 +10587,14 @@
       <c r="AE22" s="13">
         <v>0</v>
       </c>
+      <c r="AF22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="14"/>
       <c r="B23" s="16">
         <v>6</v>
@@ -10561,15 +10605,11 @@
       <c r="D23" s="13">
         <v>0</v>
       </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
+      <c r="E23" s="13"/>
       <c r="F23" s="13">
         <v>0</v>
       </c>
-      <c r="G23" s="13">
-        <v>0</v>
-      </c>
+      <c r="G23" s="13"/>
       <c r="H23" s="13">
         <v>0</v>
       </c>
@@ -10607,16 +10647,16 @@
         <v>0</v>
       </c>
       <c r="T23" s="13">
+        <v>0</v>
+      </c>
+      <c r="U23" s="13">
+        <v>0</v>
+      </c>
+      <c r="V23" s="13">
         <v>1</v>
       </c>
-      <c r="U23" s="13">
-        <v>0</v>
-      </c>
-      <c r="V23" s="13">
-        <v>0</v>
-      </c>
       <c r="W23" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" s="13">
         <v>0</v>
@@ -10642,8 +10682,14 @@
       <c r="AE23" s="13">
         <v>0</v>
       </c>
+      <c r="AF23" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="14"/>
       <c r="B24" s="16"/>
       <c r="C24">
@@ -10652,15 +10698,11 @@
       <c r="D24" s="13">
         <v>0</v>
       </c>
-      <c r="E24" s="13">
-        <v>0</v>
-      </c>
+      <c r="E24" s="13"/>
       <c r="F24" s="13">
         <v>0</v>
       </c>
-      <c r="G24" s="13">
-        <v>0</v>
-      </c>
+      <c r="G24" s="13"/>
       <c r="H24" s="13">
         <v>0</v>
       </c>
@@ -10698,14 +10740,14 @@
         <v>0</v>
       </c>
       <c r="T24" s="13">
+        <v>0</v>
+      </c>
+      <c r="U24" s="13">
+        <v>0</v>
+      </c>
+      <c r="V24" s="13">
         <v>1</v>
       </c>
-      <c r="U24" s="13">
-        <v>0</v>
-      </c>
-      <c r="V24" s="13">
-        <v>0</v>
-      </c>
       <c r="W24" s="13">
         <v>0</v>
       </c>
@@ -10733,8 +10775,14 @@
       <c r="AE24" s="13">
         <v>0</v>
       </c>
+      <c r="AF24" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="14"/>
       <c r="B25" s="16"/>
       <c r="C25">
@@ -10743,15 +10791,11 @@
       <c r="D25" s="13">
         <v>0</v>
       </c>
-      <c r="E25" s="13">
-        <v>0</v>
-      </c>
+      <c r="E25" s="13"/>
       <c r="F25" s="13">
         <v>0</v>
       </c>
-      <c r="G25" s="13">
-        <v>0</v>
-      </c>
+      <c r="G25" s="13"/>
       <c r="H25" s="13">
         <v>0</v>
       </c>
@@ -10786,17 +10830,17 @@
         <v>0</v>
       </c>
       <c r="S25" s="13">
+        <v>0</v>
+      </c>
+      <c r="T25" s="13">
+        <v>0</v>
+      </c>
+      <c r="U25" s="13">
         <v>1</v>
       </c>
-      <c r="T25" s="13">
+      <c r="V25" s="13">
         <v>1</v>
       </c>
-      <c r="U25" s="13">
-        <v>0</v>
-      </c>
-      <c r="V25" s="13">
-        <v>0</v>
-      </c>
       <c r="W25" s="13">
         <v>0</v>
       </c>
@@ -10824,8 +10868,14 @@
       <c r="AE25" s="13">
         <v>0</v>
       </c>
+      <c r="AF25" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
       <c r="B26" s="16"/>
       <c r="C26">
@@ -10834,15 +10884,11 @@
       <c r="D26" s="13">
         <v>0</v>
       </c>
-      <c r="E26" s="13">
-        <v>0</v>
-      </c>
+      <c r="E26" s="13"/>
       <c r="F26" s="13">
         <v>0</v>
       </c>
-      <c r="G26" s="13">
-        <v>0</v>
-      </c>
+      <c r="G26" s="13"/>
       <c r="H26" s="13">
         <v>0</v>
       </c>
@@ -10877,14 +10923,14 @@
         <v>0</v>
       </c>
       <c r="S26" s="13">
+        <v>0</v>
+      </c>
+      <c r="T26" s="13">
+        <v>0</v>
+      </c>
+      <c r="U26" s="13">
         <v>1</v>
       </c>
-      <c r="T26" s="13">
-        <v>0</v>
-      </c>
-      <c r="U26" s="13">
-        <v>0</v>
-      </c>
       <c r="V26" s="13">
         <v>0</v>
       </c>
@@ -10915,8 +10961,14 @@
       <c r="AE26" s="13">
         <v>0</v>
       </c>
+      <c r="AF26" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="16">
         <v>7</v>
@@ -10927,15 +10979,11 @@
       <c r="D27" s="13">
         <v>0</v>
       </c>
-      <c r="E27" s="13">
-        <v>0</v>
-      </c>
+      <c r="E27" s="13"/>
       <c r="F27" s="13">
         <v>0</v>
       </c>
-      <c r="G27" s="13">
-        <v>0</v>
-      </c>
+      <c r="G27" s="13"/>
       <c r="H27" s="13">
         <v>0</v>
       </c>
@@ -10967,17 +11015,17 @@
         <v>0</v>
       </c>
       <c r="R27" s="13">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
+        <v>0</v>
+      </c>
+      <c r="T27" s="13">
         <v>1</v>
       </c>
-      <c r="S27" s="13">
+      <c r="U27" s="13">
         <v>1</v>
       </c>
-      <c r="T27" s="13">
-        <v>0</v>
-      </c>
-      <c r="U27" s="13">
-        <v>0</v>
-      </c>
       <c r="V27" s="13">
         <v>0</v>
       </c>
@@ -11008,8 +11056,14 @@
       <c r="AE27" s="13">
         <v>0</v>
       </c>
+      <c r="AF27" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="16"/>
       <c r="C28">
@@ -11018,15 +11072,11 @@
       <c r="D28" s="13">
         <v>0</v>
       </c>
-      <c r="E28" s="13">
-        <v>0</v>
-      </c>
+      <c r="E28" s="13"/>
       <c r="F28" s="13">
         <v>0</v>
       </c>
-      <c r="G28" s="13">
-        <v>0</v>
-      </c>
+      <c r="G28" s="13"/>
       <c r="H28" s="13">
         <v>0</v>
       </c>
@@ -11058,14 +11108,14 @@
         <v>0</v>
       </c>
       <c r="R28" s="13">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
+        <v>0</v>
+      </c>
+      <c r="T28" s="13">
         <v>1</v>
       </c>
-      <c r="S28" s="13">
-        <v>0</v>
-      </c>
-      <c r="T28" s="13">
-        <v>0</v>
-      </c>
       <c r="U28" s="13">
         <v>0</v>
       </c>
@@ -11099,8 +11149,14 @@
       <c r="AE28" s="13">
         <v>0</v>
       </c>
+      <c r="AF28" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="16"/>
       <c r="C29">
@@ -11109,15 +11165,11 @@
       <c r="D29" s="13">
         <v>0</v>
       </c>
-      <c r="E29" s="13">
-        <v>0</v>
-      </c>
+      <c r="E29" s="13"/>
       <c r="F29" s="13">
         <v>0</v>
       </c>
-      <c r="G29" s="13">
-        <v>0</v>
-      </c>
+      <c r="G29" s="13"/>
       <c r="H29" s="13">
         <v>0</v>
       </c>
@@ -11146,17 +11198,17 @@
         <v>0</v>
       </c>
       <c r="Q29" s="13">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <v>1</v>
       </c>
-      <c r="R29" s="13">
+      <c r="T29" s="13">
         <v>1</v>
       </c>
-      <c r="S29" s="13">
-        <v>0</v>
-      </c>
-      <c r="T29" s="13">
-        <v>0</v>
-      </c>
       <c r="U29" s="13">
         <v>0</v>
       </c>
@@ -11190,8 +11242,14 @@
       <c r="AE29" s="13">
         <v>0</v>
       </c>
+      <c r="AF29" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="16"/>
       <c r="C30">
@@ -11200,15 +11258,11 @@
       <c r="D30" s="13">
         <v>0</v>
       </c>
-      <c r="E30" s="13">
-        <v>0</v>
-      </c>
+      <c r="E30" s="13"/>
       <c r="F30" s="13">
         <v>0</v>
       </c>
-      <c r="G30" s="13">
-        <v>0</v>
-      </c>
+      <c r="G30" s="13"/>
       <c r="H30" s="13">
         <v>0</v>
       </c>
@@ -11237,14 +11291,14 @@
         <v>0</v>
       </c>
       <c r="Q30" s="13">
+        <v>0</v>
+      </c>
+      <c r="R30" s="13">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
         <v>1</v>
       </c>
-      <c r="R30" s="13">
-        <v>0</v>
-      </c>
-      <c r="S30" s="13">
-        <v>0</v>
-      </c>
       <c r="T30" s="13">
         <v>0</v>
       </c>
@@ -11281,8 +11335,14 @@
       <c r="AE30" s="13">
         <v>0</v>
       </c>
+      <c r="AF30" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="16">
         <v>8</v>
@@ -11293,15 +11353,11 @@
       <c r="D31" s="13">
         <v>0</v>
       </c>
-      <c r="E31" s="13">
-        <v>0</v>
-      </c>
+      <c r="E31" s="13"/>
       <c r="F31" s="13">
         <v>0</v>
       </c>
-      <c r="G31" s="13">
-        <v>0</v>
-      </c>
+      <c r="G31" s="13"/>
       <c r="H31" s="13">
         <v>0</v>
       </c>
@@ -11327,17 +11383,17 @@
         <v>0</v>
       </c>
       <c r="P31" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="13">
+        <v>0</v>
+      </c>
+      <c r="R31" s="13">
         <v>1</v>
       </c>
-      <c r="Q31" s="13">
+      <c r="S31" s="13">
         <v>1</v>
       </c>
-      <c r="R31" s="13">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13">
-        <v>0</v>
-      </c>
       <c r="T31" s="13">
         <v>0</v>
       </c>
@@ -11374,8 +11430,14 @@
       <c r="AE31" s="13">
         <v>0</v>
       </c>
+      <c r="AF31" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
       <c r="B32" s="16"/>
       <c r="C32">
@@ -11384,15 +11446,11 @@
       <c r="D32" s="13">
         <v>0</v>
       </c>
-      <c r="E32" s="13">
-        <v>0</v>
-      </c>
+      <c r="E32" s="13"/>
       <c r="F32" s="13">
         <v>0</v>
       </c>
-      <c r="G32" s="13">
-        <v>0</v>
-      </c>
+      <c r="G32" s="13"/>
       <c r="H32" s="13">
         <v>0</v>
       </c>
@@ -11418,14 +11476,14 @@
         <v>0</v>
       </c>
       <c r="P32" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="13">
+        <v>0</v>
+      </c>
+      <c r="R32" s="13">
         <v>1</v>
       </c>
-      <c r="Q32" s="13">
-        <v>0</v>
-      </c>
-      <c r="R32" s="13">
-        <v>0</v>
-      </c>
       <c r="S32" s="13">
         <v>0</v>
       </c>
@@ -11465,8 +11523,14 @@
       <c r="AE32" s="13">
         <v>0</v>
       </c>
+      <c r="AF32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
       <c r="B33" s="16"/>
       <c r="C33">
@@ -11475,15 +11539,11 @@
       <c r="D33" s="13">
         <v>0</v>
       </c>
-      <c r="E33" s="13">
-        <v>0</v>
-      </c>
+      <c r="E33" s="13"/>
       <c r="F33" s="13">
         <v>0</v>
       </c>
-      <c r="G33" s="13">
-        <v>0</v>
-      </c>
+      <c r="G33" s="13"/>
       <c r="H33" s="13">
         <v>0</v>
       </c>
@@ -11509,14 +11569,14 @@
         <v>0</v>
       </c>
       <c r="P33" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="13">
+        <v>0</v>
+      </c>
+      <c r="R33" s="13">
         <v>1</v>
       </c>
-      <c r="Q33" s="13">
-        <v>0</v>
-      </c>
-      <c r="R33" s="13">
-        <v>0</v>
-      </c>
       <c r="S33" s="13">
         <v>0</v>
       </c>
@@ -11556,8 +11616,14 @@
       <c r="AE33" s="13">
         <v>0</v>
       </c>
+      <c r="AF33" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="14"/>
       <c r="B34" s="16"/>
       <c r="C34">
@@ -11566,15 +11632,11 @@
       <c r="D34" s="13">
         <v>0</v>
       </c>
-      <c r="E34" s="13">
-        <v>0</v>
-      </c>
+      <c r="E34" s="13"/>
       <c r="F34" s="13">
         <v>0</v>
       </c>
-      <c r="G34" s="13">
-        <v>0</v>
-      </c>
+      <c r="G34" s="13"/>
       <c r="H34" s="13">
         <v>0</v>
       </c>
@@ -11647,8 +11709,14 @@
       <c r="AE34" s="13">
         <v>0</v>
       </c>
+      <c r="AF34" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="16">
         <v>9</v>
@@ -11659,15 +11727,11 @@
       <c r="D35" s="13">
         <v>0</v>
       </c>
-      <c r="E35" s="13">
-        <v>0</v>
-      </c>
+      <c r="E35" s="13"/>
       <c r="F35" s="13">
         <v>0</v>
       </c>
-      <c r="G35" s="13">
-        <v>0</v>
-      </c>
+      <c r="G35" s="13"/>
       <c r="H35" s="13">
         <v>0</v>
       </c>
@@ -11740,8 +11804,14 @@
       <c r="AE35" s="13">
         <v>0</v>
       </c>
+      <c r="AF35" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="14"/>
       <c r="B36" s="16"/>
       <c r="C36">
@@ -11750,15 +11820,11 @@
       <c r="D36" s="13">
         <v>0</v>
       </c>
-      <c r="E36" s="13">
-        <v>0</v>
-      </c>
+      <c r="E36" s="13"/>
       <c r="F36" s="13">
         <v>0</v>
       </c>
-      <c r="G36" s="13">
-        <v>0</v>
-      </c>
+      <c r="G36" s="13"/>
       <c r="H36" s="13">
         <v>0</v>
       </c>
@@ -11831,8 +11897,14 @@
       <c r="AE36" s="13">
         <v>0</v>
       </c>
+      <c r="AF36" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="14"/>
       <c r="B37" s="16"/>
       <c r="C37">
@@ -11841,15 +11913,11 @@
       <c r="D37" s="13">
         <v>0</v>
       </c>
-      <c r="E37" s="13">
-        <v>0</v>
-      </c>
+      <c r="E37" s="13"/>
       <c r="F37" s="13">
         <v>0</v>
       </c>
-      <c r="G37" s="13">
-        <v>0</v>
-      </c>
+      <c r="G37" s="13"/>
       <c r="H37" s="13">
         <v>0</v>
       </c>
@@ -11922,8 +11990,14 @@
       <c r="AE37" s="13">
         <v>0</v>
       </c>
+      <c r="AF37" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="14"/>
       <c r="B38" s="16"/>
       <c r="C38">
@@ -11932,15 +12006,11 @@
       <c r="D38" s="13">
         <v>0</v>
       </c>
-      <c r="E38" s="13">
-        <v>0</v>
-      </c>
+      <c r="E38" s="13"/>
       <c r="F38" s="13">
         <v>0</v>
       </c>
-      <c r="G38" s="13">
-        <v>0</v>
-      </c>
+      <c r="G38" s="13"/>
       <c r="H38" s="13">
         <v>0</v>
       </c>
@@ -12013,8 +12083,14 @@
       <c r="AE38" s="13">
         <v>0</v>
       </c>
+      <c r="AF38" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="14"/>
       <c r="B39" s="16">
         <v>10</v>
@@ -12025,15 +12101,11 @@
       <c r="D39" s="13">
         <v>0</v>
       </c>
-      <c r="E39" s="13">
-        <v>0</v>
-      </c>
+      <c r="E39" s="13"/>
       <c r="F39" s="13">
         <v>0</v>
       </c>
-      <c r="G39" s="13">
-        <v>0</v>
-      </c>
+      <c r="G39" s="13"/>
       <c r="H39" s="13">
         <v>0</v>
       </c>
@@ -12106,8 +12178,14 @@
       <c r="AE39" s="13">
         <v>0</v>
       </c>
+      <c r="AF39" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="14"/>
       <c r="B40" s="16"/>
       <c r="C40">
@@ -12116,15 +12194,11 @@
       <c r="D40" s="13">
         <v>0</v>
       </c>
-      <c r="E40" s="13">
-        <v>0</v>
-      </c>
+      <c r="E40" s="13"/>
       <c r="F40" s="13">
         <v>0</v>
       </c>
-      <c r="G40" s="13">
-        <v>0</v>
-      </c>
+      <c r="G40" s="13"/>
       <c r="H40" s="13">
         <v>0</v>
       </c>
@@ -12197,8 +12271,14 @@
       <c r="AE40" s="13">
         <v>0</v>
       </c>
+      <c r="AF40" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="14"/>
       <c r="B41" s="16"/>
       <c r="C41">
@@ -12207,15 +12287,11 @@
       <c r="D41" s="13">
         <v>0</v>
       </c>
-      <c r="E41" s="13">
-        <v>0</v>
-      </c>
+      <c r="E41" s="13"/>
       <c r="F41" s="13">
         <v>0</v>
       </c>
-      <c r="G41" s="13">
-        <v>0</v>
-      </c>
+      <c r="G41" s="13"/>
       <c r="H41" s="13">
         <v>0</v>
       </c>
@@ -12288,8 +12364,14 @@
       <c r="AE41" s="13">
         <v>0</v>
       </c>
+      <c r="AF41" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="14"/>
       <c r="B42" s="16"/>
       <c r="C42">
@@ -12298,15 +12380,11 @@
       <c r="D42" s="13">
         <v>0</v>
       </c>
-      <c r="E42" s="13">
-        <v>0</v>
-      </c>
+      <c r="E42" s="13"/>
       <c r="F42" s="13">
         <v>0</v>
       </c>
-      <c r="G42" s="13">
-        <v>0</v>
-      </c>
+      <c r="G42" s="13"/>
       <c r="H42" s="13">
         <v>0</v>
       </c>
@@ -12377,6 +12455,12 @@
         <v>0</v>
       </c>
       <c r="AE42" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="13">
         <v>0</v>
       </c>
     </row>
@@ -12386,7 +12470,7 @@
     <mergeCell ref="B31:B34"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="B39:B42"/>
-    <mergeCell ref="D1:AE1"/>
+    <mergeCell ref="D1:AG1"/>
     <mergeCell ref="A3:A42"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B10"/>
@@ -12395,7 +12479,7 @@
     <mergeCell ref="B19:B22"/>
     <mergeCell ref="B23:B26"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:AE42">
+  <conditionalFormatting sqref="D3:AG42">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -12709,111 +12793,111 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <f>+raw!E3</f>
+        <f>+raw!F3</f>
         <v>0</v>
       </c>
       <c r="F3">
-        <f>+raw!F3</f>
+        <f>+raw!H3</f>
         <v>0</v>
       </c>
       <c r="H3">
-        <f>+raw!G3</f>
+        <f>+raw!I3</f>
         <v>0</v>
       </c>
       <c r="J3">
-        <f>+raw!H3</f>
+        <f>+raw!J3</f>
         <v>0</v>
       </c>
       <c r="L3">
-        <f>+raw!I3</f>
+        <f>+raw!K3</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>+raw!J3</f>
+        <f>+raw!L3</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>+raw!K3</f>
+        <f>+raw!M3</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>+raw!L3</f>
+        <f>+raw!N3</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>+raw!M3</f>
+        <f>+raw!O3</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>+raw!N3</f>
+        <f>+raw!P3</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>+raw!O3</f>
+        <f>+raw!Q3</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>+raw!P3</f>
+        <f>+raw!R3</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>+raw!Q3</f>
+        <f>+raw!S3</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>+raw!R3</f>
+        <f>+raw!T3</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>+raw!S3</f>
+        <f>+raw!U3</f>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f>+raw!T3</f>
+        <f>+raw!V3</f>
         <v>0</v>
       </c>
       <c r="AJ3">
-        <f>+raw!U3</f>
+        <f>+raw!W3</f>
         <v>0</v>
       </c>
       <c r="AL3">
-        <f>+raw!V3</f>
+        <f>+raw!X3</f>
         <v>0</v>
       </c>
       <c r="AN3">
-        <f>+raw!W3</f>
+        <f>+raw!Y3</f>
         <v>0</v>
       </c>
       <c r="AP3">
-        <f>+raw!X3</f>
+        <f>+raw!Z3</f>
         <v>0</v>
       </c>
       <c r="AR3">
-        <f>+raw!Y3</f>
+        <f>+raw!AA3</f>
         <v>0</v>
       </c>
       <c r="AT3">
-        <f>+raw!Z3</f>
+        <f>+raw!AB3</f>
         <v>0</v>
       </c>
       <c r="AV3">
-        <f>+raw!AA3</f>
+        <f>+raw!AC3</f>
         <v>0</v>
       </c>
       <c r="AX3">
-        <f>+raw!AB3</f>
+        <f>+raw!AD3</f>
         <v>0</v>
       </c>
       <c r="AZ3">
-        <f>+raw!AC3</f>
+        <f>+raw!AE3</f>
         <v>0</v>
       </c>
       <c r="BB3">
-        <f>+raw!AD3</f>
+        <f>+raw!AF3</f>
         <v>0</v>
       </c>
       <c r="BD3">
-        <f>+raw!AE3</f>
+        <f>+raw!AG3</f>
         <v>0</v>
       </c>
     </row>
@@ -12823,111 +12907,111 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <f>+raw!E4</f>
+        <f>+raw!F4</f>
         <v>0</v>
       </c>
       <c r="G4">
-        <f>+raw!F4</f>
+        <f>+raw!H4</f>
         <v>0</v>
       </c>
       <c r="I4">
-        <f>+raw!G4</f>
+        <f>+raw!I4</f>
         <v>0</v>
       </c>
       <c r="K4">
-        <f>+raw!H4</f>
+        <f>+raw!J4</f>
         <v>0</v>
       </c>
       <c r="M4">
-        <f>+raw!I4</f>
+        <f>+raw!K4</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>+raw!J4</f>
+        <f>+raw!L4</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>+raw!K4</f>
+        <f>+raw!M4</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>+raw!L4</f>
+        <f>+raw!N4</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>+raw!M4</f>
+        <f>+raw!O4</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>+raw!N4</f>
+        <f>+raw!P4</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>+raw!O4</f>
+        <f>+raw!Q4</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>+raw!P4</f>
+        <f>+raw!R4</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>+raw!Q4</f>
+        <f>+raw!S4</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>+raw!R4</f>
+        <f>+raw!T4</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>+raw!S4</f>
+        <f>+raw!U4</f>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f>+raw!T4</f>
+        <f>+raw!V4</f>
         <v>0</v>
       </c>
       <c r="AK4">
-        <f>+raw!U4</f>
+        <f>+raw!W4</f>
         <v>0</v>
       </c>
       <c r="AM4">
-        <f>+raw!V4</f>
+        <f>+raw!X4</f>
         <v>0</v>
       </c>
       <c r="AO4">
-        <f>+raw!W4</f>
+        <f>+raw!Y4</f>
         <v>0</v>
       </c>
       <c r="AQ4">
-        <f>+raw!X4</f>
+        <f>+raw!Z4</f>
         <v>0</v>
       </c>
       <c r="AS4">
-        <f>+raw!Y4</f>
+        <f>+raw!AA4</f>
         <v>0</v>
       </c>
       <c r="AU4">
-        <f>+raw!Z4</f>
+        <f>+raw!AB4</f>
         <v>0</v>
       </c>
       <c r="AW4">
-        <f>+raw!AA4</f>
+        <f>+raw!AC4</f>
         <v>0</v>
       </c>
       <c r="AY4">
-        <f>+raw!AB4</f>
+        <f>+raw!AD4</f>
         <v>0</v>
       </c>
       <c r="BA4">
-        <f>+raw!AC4</f>
+        <f>+raw!AE4</f>
         <v>0</v>
       </c>
       <c r="BC4">
-        <f>+raw!AD4</f>
+        <f>+raw!AF4</f>
         <v>0</v>
       </c>
       <c r="BE4">
-        <f>+raw!AE4</f>
+        <f>+raw!AG4</f>
         <v>0</v>
       </c>
     </row>
@@ -12937,111 +13021,111 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <f>+raw!E5</f>
+        <f>+raw!F5</f>
         <v>0</v>
       </c>
       <c r="H5">
-        <f>+raw!F5</f>
+        <f>+raw!H5</f>
         <v>0</v>
       </c>
       <c r="J5">
-        <f>+raw!G5</f>
+        <f>+raw!I5</f>
         <v>0</v>
       </c>
       <c r="L5">
-        <f>+raw!H5</f>
+        <f>+raw!J5</f>
         <v>0</v>
       </c>
       <c r="N5">
-        <f>+raw!I5</f>
+        <f>+raw!K5</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>+raw!J5</f>
+        <f>+raw!L5</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>+raw!K5</f>
+        <f>+raw!M5</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>+raw!L5</f>
+        <f>+raw!N5</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>+raw!M5</f>
+        <f>+raw!O5</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>+raw!N5</f>
+        <f>+raw!P5</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>+raw!O5</f>
+        <f>+raw!Q5</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>+raw!P5</f>
+        <f>+raw!R5</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>+raw!Q5</f>
+        <f>+raw!S5</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>+raw!R5</f>
+        <f>+raw!T5</f>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f>+raw!S5</f>
+        <f>+raw!U5</f>
         <v>0</v>
       </c>
       <c r="AJ5">
-        <f>+raw!T5</f>
+        <f>+raw!V5</f>
         <v>0</v>
       </c>
       <c r="AL5">
-        <f>+raw!U5</f>
+        <f>+raw!W5</f>
         <v>0</v>
       </c>
       <c r="AN5">
-        <f>+raw!V5</f>
+        <f>+raw!X5</f>
         <v>0</v>
       </c>
       <c r="AP5">
-        <f>+raw!W5</f>
+        <f>+raw!Y5</f>
         <v>0</v>
       </c>
       <c r="AR5">
-        <f>+raw!X5</f>
+        <f>+raw!Z5</f>
         <v>0</v>
       </c>
       <c r="AT5">
-        <f>+raw!Y5</f>
+        <f>+raw!AA5</f>
         <v>0</v>
       </c>
       <c r="AV5">
-        <f>+raw!Z5</f>
+        <f>+raw!AB5</f>
         <v>0</v>
       </c>
       <c r="AX5">
-        <f>+raw!AA5</f>
+        <f>+raw!AC5</f>
         <v>0</v>
       </c>
       <c r="AZ5">
-        <f>+raw!AB5</f>
+        <f>+raw!AD5</f>
         <v>0</v>
       </c>
       <c r="BB5">
-        <f>+raw!AC5</f>
+        <f>+raw!AE5</f>
         <v>0</v>
       </c>
       <c r="BD5">
-        <f>+raw!AD5</f>
+        <f>+raw!AF5</f>
         <v>0</v>
       </c>
       <c r="BF5">
-        <f>+raw!AE5</f>
+        <f>+raw!AG5</f>
         <v>0</v>
       </c>
     </row>
@@ -13051,111 +13135,111 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <f>+raw!E6</f>
+        <f>+raw!F6</f>
         <v>0</v>
       </c>
       <c r="I6">
-        <f>+raw!F6</f>
+        <f>+raw!H6</f>
         <v>0</v>
       </c>
       <c r="K6">
-        <f>+raw!G6</f>
+        <f>+raw!I6</f>
         <v>0</v>
       </c>
       <c r="M6">
-        <f>+raw!H6</f>
+        <f>+raw!J6</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>+raw!I6</f>
+        <f>+raw!K6</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>+raw!J6</f>
+        <f>+raw!L6</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>+raw!K6</f>
+        <f>+raw!M6</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>+raw!L6</f>
+        <f>+raw!N6</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>+raw!M6</f>
+        <f>+raw!O6</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>+raw!N6</f>
+        <f>+raw!P6</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>+raw!O6</f>
+        <f>+raw!Q6</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>+raw!P6</f>
+        <f>+raw!R6</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>+raw!Q6</f>
+        <f>+raw!S6</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>+raw!R6</f>
+        <f>+raw!T6</f>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f>+raw!S6</f>
+        <f>+raw!U6</f>
         <v>0</v>
       </c>
       <c r="AK6">
-        <f>+raw!T6</f>
+        <f>+raw!V6</f>
         <v>0</v>
       </c>
       <c r="AM6">
-        <f>+raw!U6</f>
+        <f>+raw!W6</f>
         <v>0</v>
       </c>
       <c r="AO6">
-        <f>+raw!V6</f>
+        <f>+raw!X6</f>
         <v>0</v>
       </c>
       <c r="AQ6">
-        <f>+raw!W6</f>
+        <f>+raw!Y6</f>
         <v>0</v>
       </c>
       <c r="AS6">
-        <f>+raw!X6</f>
+        <f>+raw!Z6</f>
         <v>0</v>
       </c>
       <c r="AU6">
-        <f>+raw!Y6</f>
+        <f>+raw!AA6</f>
         <v>0</v>
       </c>
       <c r="AW6">
-        <f>+raw!Z6</f>
+        <f>+raw!AB6</f>
         <v>0</v>
       </c>
       <c r="AY6">
-        <f>+raw!AA6</f>
+        <f>+raw!AC6</f>
         <v>0</v>
       </c>
       <c r="BA6">
-        <f>+raw!AB6</f>
+        <f>+raw!AD6</f>
         <v>0</v>
       </c>
       <c r="BC6">
-        <f>+raw!AC6</f>
+        <f>+raw!AE6</f>
         <v>0</v>
       </c>
       <c r="BE6">
-        <f>+raw!AD6</f>
+        <f>+raw!AF6</f>
         <v>0</v>
       </c>
       <c r="BG6">
-        <f>+raw!AE6</f>
+        <f>+raw!AG6</f>
         <v>0</v>
       </c>
     </row>
@@ -13165,111 +13249,111 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <f>+raw!E7</f>
+        <f>+raw!F7</f>
         <v>0</v>
       </c>
       <c r="J7">
-        <f>+raw!F7</f>
+        <f>+raw!H7</f>
         <v>0</v>
       </c>
       <c r="L7">
-        <f>+raw!G7</f>
+        <f>+raw!I7</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f>+raw!H7</f>
+        <f>+raw!J7</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>+raw!I7</f>
+        <f>+raw!K7</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>+raw!J7</f>
+        <f>+raw!L7</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>+raw!K7</f>
+        <f>+raw!M7</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>+raw!L7</f>
+        <f>+raw!N7</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>+raw!M7</f>
+        <f>+raw!O7</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>+raw!N7</f>
+        <f>+raw!P7</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>+raw!O7</f>
+        <f>+raw!Q7</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>+raw!P7</f>
+        <f>+raw!R7</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>+raw!Q7</f>
+        <f>+raw!S7</f>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f>+raw!R7</f>
+        <f>+raw!T7</f>
         <v>0</v>
       </c>
       <c r="AJ7">
-        <f>+raw!S7</f>
+        <f>+raw!U7</f>
         <v>0</v>
       </c>
       <c r="AL7">
-        <f>+raw!T7</f>
+        <f>+raw!V7</f>
         <v>0</v>
       </c>
       <c r="AN7">
-        <f>+raw!U7</f>
+        <f>+raw!W7</f>
         <v>0</v>
       </c>
       <c r="AP7">
-        <f>+raw!V7</f>
+        <f>+raw!X7</f>
         <v>0</v>
       </c>
       <c r="AR7">
-        <f>+raw!W7</f>
+        <f>+raw!Y7</f>
         <v>0</v>
       </c>
       <c r="AT7">
-        <f>+raw!X7</f>
+        <f>+raw!Z7</f>
         <v>0</v>
       </c>
       <c r="AV7">
-        <f>+raw!Y7</f>
+        <f>+raw!AA7</f>
         <v>0</v>
       </c>
       <c r="AX7">
-        <f>+raw!Z7</f>
+        <f>+raw!AB7</f>
         <v>0</v>
       </c>
       <c r="AZ7">
-        <f>+raw!AA7</f>
+        <f>+raw!AC7</f>
         <v>0</v>
       </c>
       <c r="BB7">
-        <f>+raw!AB7</f>
+        <f>+raw!AD7</f>
         <v>0</v>
       </c>
       <c r="BD7">
-        <f>+raw!AC7</f>
+        <f>+raw!AE7</f>
         <v>0</v>
       </c>
       <c r="BF7">
-        <f>+raw!AD7</f>
+        <f>+raw!AF7</f>
         <v>0</v>
       </c>
       <c r="BH7">
-        <f>+raw!AE7</f>
+        <f>+raw!AG7</f>
         <v>0</v>
       </c>
     </row>
@@ -13279,111 +13363,111 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <f>+raw!E8</f>
+        <f>+raw!F8</f>
         <v>0</v>
       </c>
       <c r="K8">
-        <f>+raw!F8</f>
+        <f>+raw!H8</f>
         <v>0</v>
       </c>
       <c r="M8">
-        <f>+raw!G8</f>
+        <f>+raw!I8</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>+raw!H8</f>
+        <f>+raw!J8</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>+raw!I8</f>
+        <f>+raw!K8</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>+raw!J8</f>
+        <f>+raw!L8</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>+raw!K8</f>
+        <f>+raw!M8</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>+raw!L8</f>
+        <f>+raw!N8</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>+raw!M8</f>
+        <f>+raw!O8</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>+raw!N8</f>
+        <f>+raw!P8</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>+raw!O8</f>
+        <f>+raw!Q8</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>+raw!P8</f>
+        <f>+raw!R8</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>+raw!Q8</f>
+        <f>+raw!S8</f>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f>+raw!R8</f>
+        <f>+raw!T8</f>
         <v>0</v>
       </c>
       <c r="AK8">
-        <f>+raw!S8</f>
+        <f>+raw!U8</f>
         <v>0</v>
       </c>
       <c r="AM8">
-        <f>+raw!T8</f>
+        <f>+raw!V8</f>
         <v>0</v>
       </c>
       <c r="AO8">
-        <f>+raw!U8</f>
+        <f>+raw!W8</f>
         <v>0</v>
       </c>
       <c r="AQ8">
-        <f>+raw!V8</f>
+        <f>+raw!X8</f>
         <v>0</v>
       </c>
       <c r="AS8">
-        <f>+raw!W8</f>
+        <f>+raw!Y8</f>
         <v>0</v>
       </c>
       <c r="AU8">
-        <f>+raw!X8</f>
+        <f>+raw!Z8</f>
         <v>0</v>
       </c>
       <c r="AW8">
-        <f>+raw!Y8</f>
+        <f>+raw!AA8</f>
         <v>0</v>
       </c>
       <c r="AY8">
-        <f>+raw!Z8</f>
+        <f>+raw!AB8</f>
         <v>0</v>
       </c>
       <c r="BA8">
-        <f>+raw!AA8</f>
+        <f>+raw!AC8</f>
         <v>0</v>
       </c>
       <c r="BC8">
-        <f>+raw!AB8</f>
+        <f>+raw!AD8</f>
         <v>0</v>
       </c>
       <c r="BE8">
-        <f>+raw!AC8</f>
+        <f>+raw!AE8</f>
         <v>0</v>
       </c>
       <c r="BG8">
-        <f>+raw!AD8</f>
+        <f>+raw!AF8</f>
         <v>0</v>
       </c>
       <c r="BI8">
-        <f>+raw!AE8</f>
+        <f>+raw!AG8</f>
         <v>0</v>
       </c>
     </row>
@@ -13393,111 +13477,111 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <f>+raw!E9</f>
+        <f>+raw!F9</f>
         <v>0</v>
       </c>
       <c r="L9">
-        <f>+raw!F9</f>
+        <f>+raw!H9</f>
         <v>0</v>
       </c>
       <c r="N9">
-        <f>+raw!G9</f>
+        <f>+raw!I9</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>+raw!H9</f>
+        <f>+raw!J9</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>+raw!I9</f>
+        <f>+raw!K9</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>+raw!J9</f>
+        <f>+raw!L9</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>+raw!K9</f>
+        <f>+raw!M9</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>+raw!L9</f>
+        <f>+raw!N9</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>+raw!M9</f>
+        <f>+raw!O9</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>+raw!N9</f>
+        <f>+raw!P9</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>+raw!O9</f>
+        <f>+raw!Q9</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>+raw!P9</f>
+        <f>+raw!R9</f>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f>+raw!Q9</f>
+        <f>+raw!S9</f>
         <v>0</v>
       </c>
       <c r="AJ9">
-        <f>+raw!R9</f>
+        <f>+raw!T9</f>
         <v>0</v>
       </c>
       <c r="AL9">
-        <f>+raw!S9</f>
+        <f>+raw!U9</f>
         <v>0</v>
       </c>
       <c r="AN9">
-        <f>+raw!T9</f>
+        <f>+raw!V9</f>
         <v>0</v>
       </c>
       <c r="AP9">
-        <f>+raw!U9</f>
+        <f>+raw!W9</f>
         <v>0</v>
       </c>
       <c r="AR9">
-        <f>+raw!V9</f>
+        <f>+raw!X9</f>
         <v>0</v>
       </c>
       <c r="AT9">
-        <f>+raw!W9</f>
+        <f>+raw!Y9</f>
         <v>0</v>
       </c>
       <c r="AV9">
-        <f>+raw!X9</f>
+        <f>+raw!Z9</f>
         <v>0</v>
       </c>
       <c r="AX9">
-        <f>+raw!Y9</f>
+        <f>+raw!AA9</f>
         <v>0</v>
       </c>
       <c r="AZ9">
-        <f>+raw!Z9</f>
+        <f>+raw!AB9</f>
         <v>0</v>
       </c>
       <c r="BB9">
-        <f>+raw!AA9</f>
+        <f>+raw!AC9</f>
         <v>0</v>
       </c>
       <c r="BD9">
-        <f>+raw!AB9</f>
+        <f>+raw!AD9</f>
         <v>0</v>
       </c>
       <c r="BF9">
-        <f>+raw!AC9</f>
+        <f>+raw!AE9</f>
         <v>0</v>
       </c>
       <c r="BH9">
-        <f>+raw!AD9</f>
+        <f>+raw!AF9</f>
         <v>0</v>
       </c>
       <c r="BJ9">
-        <f>+raw!AE9</f>
+        <f>+raw!AG9</f>
         <v>0</v>
       </c>
     </row>
@@ -13507,111 +13591,111 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <f>+raw!E10</f>
+        <f>+raw!F10</f>
         <v>0</v>
       </c>
       <c r="M10">
-        <f>+raw!F10</f>
+        <f>+raw!H10</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>+raw!G10</f>
+        <f>+raw!I10</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>+raw!H10</f>
+        <f>+raw!J10</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>+raw!I10</f>
+        <f>+raw!K10</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>+raw!J10</f>
+        <f>+raw!L10</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>+raw!K10</f>
+        <f>+raw!M10</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>+raw!L10</f>
+        <f>+raw!N10</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>+raw!M10</f>
+        <f>+raw!O10</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>+raw!N10</f>
+        <f>+raw!P10</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>+raw!O10</f>
+        <f>+raw!Q10</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>+raw!P10</f>
+        <f>+raw!R10</f>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f>+raw!Q10</f>
+        <f>+raw!S10</f>
         <v>0</v>
       </c>
       <c r="AK10">
-        <f>+raw!R10</f>
+        <f>+raw!T10</f>
         <v>0</v>
       </c>
       <c r="AM10">
-        <f>+raw!S10</f>
+        <f>+raw!U10</f>
         <v>0</v>
       </c>
       <c r="AO10">
-        <f>+raw!T10</f>
+        <f>+raw!V10</f>
         <v>0</v>
       </c>
       <c r="AQ10">
-        <f>+raw!U10</f>
+        <f>+raw!W10</f>
         <v>0</v>
       </c>
       <c r="AS10">
-        <f>+raw!V10</f>
+        <f>+raw!X10</f>
         <v>0</v>
       </c>
       <c r="AU10">
-        <f>+raw!W10</f>
+        <f>+raw!Y10</f>
         <v>0</v>
       </c>
       <c r="AW10">
-        <f>+raw!X10</f>
+        <f>+raw!Z10</f>
         <v>0</v>
       </c>
       <c r="AY10">
-        <f>+raw!Y10</f>
+        <f>+raw!AA10</f>
         <v>0</v>
       </c>
       <c r="BA10">
-        <f>+raw!Z10</f>
+        <f>+raw!AB10</f>
         <v>0</v>
       </c>
       <c r="BC10">
-        <f>+raw!AA10</f>
+        <f>+raw!AC10</f>
         <v>0</v>
       </c>
       <c r="BE10">
-        <f>+raw!AB10</f>
+        <f>+raw!AD10</f>
         <v>0</v>
       </c>
       <c r="BG10">
-        <f>+raw!AC10</f>
+        <f>+raw!AE10</f>
         <v>0</v>
       </c>
       <c r="BI10">
-        <f>+raw!AD10</f>
+        <f>+raw!AF10</f>
         <v>0</v>
       </c>
       <c r="BK10">
-        <f>+raw!AE10</f>
+        <f>+raw!AG10</f>
         <v>0</v>
       </c>
     </row>
@@ -13621,111 +13705,111 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <f>+raw!E11</f>
+        <f>+raw!F11</f>
         <v>0</v>
       </c>
       <c r="N11">
-        <f>+raw!F11</f>
+        <f>+raw!H11</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>+raw!G11</f>
+        <f>+raw!I11</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>+raw!H11</f>
+        <f>+raw!J11</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>+raw!I11</f>
+        <f>+raw!K11</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>+raw!J11</f>
+        <f>+raw!L11</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>+raw!K11</f>
+        <f>+raw!M11</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>+raw!L11</f>
+        <f>+raw!N11</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>+raw!M11</f>
+        <f>+raw!O11</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>+raw!N11</f>
+        <f>+raw!P11</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>+raw!O11</f>
+        <f>+raw!Q11</f>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f>+raw!P11</f>
+        <f>+raw!R11</f>
         <v>0</v>
       </c>
       <c r="AJ11">
-        <f>+raw!Q11</f>
+        <f>+raw!S11</f>
         <v>0</v>
       </c>
       <c r="AL11">
-        <f>+raw!R11</f>
+        <f>+raw!T11</f>
         <v>0</v>
       </c>
       <c r="AN11">
-        <f>+raw!S11</f>
+        <f>+raw!U11</f>
         <v>0</v>
       </c>
       <c r="AP11">
-        <f>+raw!T11</f>
+        <f>+raw!V11</f>
         <v>0</v>
       </c>
       <c r="AR11">
-        <f>+raw!U11</f>
+        <f>+raw!W11</f>
         <v>0</v>
       </c>
       <c r="AT11">
-        <f>+raw!V11</f>
+        <f>+raw!X11</f>
         <v>0</v>
       </c>
       <c r="AV11">
-        <f>+raw!W11</f>
+        <f>+raw!Y11</f>
         <v>0</v>
       </c>
       <c r="AX11">
-        <f>+raw!X11</f>
+        <f>+raw!Z11</f>
         <v>0</v>
       </c>
       <c r="AZ11">
-        <f>+raw!Y11</f>
+        <f>+raw!AA11</f>
         <v>0</v>
       </c>
       <c r="BB11">
-        <f>+raw!Z11</f>
+        <f>+raw!AB11</f>
         <v>0</v>
       </c>
       <c r="BD11">
-        <f>+raw!AA11</f>
+        <f>+raw!AC11</f>
         <v>0</v>
       </c>
       <c r="BF11">
-        <f>+raw!AB11</f>
+        <f>+raw!AD11</f>
         <v>0</v>
       </c>
       <c r="BH11">
-        <f>+raw!AC11</f>
+        <f>+raw!AE11</f>
         <v>0</v>
       </c>
       <c r="BJ11">
-        <f>+raw!AD11</f>
+        <f>+raw!AF11</f>
         <v>0</v>
       </c>
       <c r="BL11">
-        <f>+raw!AE11</f>
+        <f>+raw!AG11</f>
         <v>0</v>
       </c>
     </row>
@@ -13735,111 +13819,111 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <f>+raw!E12</f>
+        <f>+raw!F12</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>+raw!F12</f>
+        <f>+raw!H12</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>+raw!G12</f>
+        <f>+raw!I12</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>+raw!H12</f>
+        <f>+raw!J12</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>+raw!I12</f>
+        <f>+raw!K12</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>+raw!J12</f>
+        <f>+raw!L12</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>+raw!K12</f>
+        <f>+raw!M12</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>+raw!L12</f>
+        <f>+raw!N12</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>+raw!M12</f>
+        <f>+raw!O12</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>+raw!N12</f>
+        <f>+raw!P12</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>+raw!O12</f>
+        <f>+raw!Q12</f>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f>+raw!P12</f>
+        <f>+raw!R12</f>
         <v>0</v>
       </c>
       <c r="AK12">
-        <f>+raw!Q12</f>
+        <f>+raw!S12</f>
         <v>0</v>
       </c>
       <c r="AM12">
-        <f>+raw!R12</f>
+        <f>+raw!T12</f>
         <v>0</v>
       </c>
       <c r="AO12">
-        <f>+raw!S12</f>
+        <f>+raw!U12</f>
         <v>0</v>
       </c>
       <c r="AQ12">
-        <f>+raw!T12</f>
+        <f>+raw!V12</f>
         <v>0</v>
       </c>
       <c r="AS12">
-        <f>+raw!U12</f>
+        <f>+raw!W12</f>
         <v>0</v>
       </c>
       <c r="AU12">
-        <f>+raw!V12</f>
+        <f>+raw!X12</f>
         <v>0</v>
       </c>
       <c r="AW12">
-        <f>+raw!W12</f>
+        <f>+raw!Y12</f>
         <v>0</v>
       </c>
       <c r="AY12">
-        <f>+raw!X12</f>
+        <f>+raw!Z12</f>
         <v>0</v>
       </c>
       <c r="BA12">
-        <f>+raw!Y12</f>
+        <f>+raw!AA12</f>
         <v>0</v>
       </c>
       <c r="BC12">
-        <f>+raw!Z12</f>
+        <f>+raw!AB12</f>
         <v>0</v>
       </c>
       <c r="BE12">
-        <f>+raw!AA12</f>
+        <f>+raw!AC12</f>
         <v>0</v>
       </c>
       <c r="BG12">
-        <f>+raw!AB12</f>
+        <f>+raw!AD12</f>
         <v>0</v>
       </c>
       <c r="BI12">
-        <f>+raw!AC12</f>
+        <f>+raw!AE12</f>
         <v>0</v>
       </c>
       <c r="BK12">
-        <f>+raw!AD12</f>
+        <f>+raw!AF12</f>
         <v>0</v>
       </c>
       <c r="BM12">
-        <f>+raw!AE12</f>
+        <f>+raw!AG12</f>
         <v>0</v>
       </c>
     </row>
@@ -13849,111 +13933,111 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <f>+raw!E13</f>
+        <f>+raw!F13</f>
         <v>0</v>
       </c>
       <c r="P13">
-        <f>+raw!F13</f>
+        <f>+raw!H13</f>
         <v>0</v>
       </c>
       <c r="R13">
-        <f>+raw!G13</f>
+        <f>+raw!I13</f>
         <v>0</v>
       </c>
       <c r="T13">
-        <f>+raw!H13</f>
+        <f>+raw!J13</f>
         <v>0</v>
       </c>
       <c r="V13">
-        <f>+raw!I13</f>
+        <f>+raw!K13</f>
         <v>0</v>
       </c>
       <c r="X13">
-        <f>+raw!J13</f>
+        <f>+raw!L13</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>+raw!K13</f>
+        <f>+raw!M13</f>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f>+raw!L13</f>
+        <f>+raw!N13</f>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f>+raw!M13</f>
+        <f>+raw!O13</f>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f>+raw!N13</f>
+        <f>+raw!P13</f>
         <v>0</v>
       </c>
       <c r="AH13">
-        <f>+raw!O13</f>
+        <f>+raw!Q13</f>
         <v>0</v>
       </c>
       <c r="AJ13">
-        <f>+raw!P13</f>
+        <f>+raw!R13</f>
         <v>0</v>
       </c>
       <c r="AL13">
-        <f>+raw!Q13</f>
+        <f>+raw!S13</f>
         <v>0</v>
       </c>
       <c r="AN13">
-        <f>+raw!R13</f>
+        <f>+raw!T13</f>
         <v>0</v>
       </c>
       <c r="AP13">
-        <f>+raw!S13</f>
+        <f>+raw!U13</f>
         <v>0</v>
       </c>
       <c r="AR13">
-        <f>+raw!T13</f>
+        <f>+raw!V13</f>
         <v>0</v>
       </c>
       <c r="AT13">
-        <f>+raw!U13</f>
+        <f>+raw!W13</f>
         <v>0</v>
       </c>
       <c r="AV13">
-        <f>+raw!V13</f>
+        <f>+raw!X13</f>
         <v>0</v>
       </c>
       <c r="AX13">
-        <f>+raw!W13</f>
+        <f>+raw!Y13</f>
         <v>0</v>
       </c>
       <c r="AZ13">
-        <f>+raw!X13</f>
+        <f>+raw!Z13</f>
         <v>0</v>
       </c>
       <c r="BB13">
-        <f>+raw!Y13</f>
+        <f>+raw!AA13</f>
         <v>0</v>
       </c>
       <c r="BD13">
-        <f>+raw!Z13</f>
+        <f>+raw!AB13</f>
         <v>0</v>
       </c>
       <c r="BF13">
-        <f>+raw!AA13</f>
+        <f>+raw!AC13</f>
         <v>0</v>
       </c>
       <c r="BH13">
-        <f>+raw!AB13</f>
+        <f>+raw!AD13</f>
         <v>0</v>
       </c>
       <c r="BJ13">
-        <f>+raw!AC13</f>
+        <f>+raw!AE13</f>
         <v>0</v>
       </c>
       <c r="BL13">
-        <f>+raw!AD13</f>
+        <f>+raw!AF13</f>
         <v>0</v>
       </c>
       <c r="BN13">
-        <f>+raw!AE13</f>
+        <f>+raw!AG13</f>
         <v>0</v>
       </c>
     </row>
@@ -13963,111 +14047,111 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <f>+raw!E14</f>
+        <f>+raw!F14</f>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>+raw!F14</f>
+        <f>+raw!H14</f>
         <v>0</v>
       </c>
       <c r="S14">
-        <f>+raw!G14</f>
+        <f>+raw!I14</f>
         <v>0</v>
       </c>
       <c r="U14">
-        <f>+raw!H14</f>
+        <f>+raw!J14</f>
         <v>0</v>
       </c>
       <c r="W14">
-        <f>+raw!I14</f>
+        <f>+raw!K14</f>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f>+raw!J14</f>
+        <f>+raw!L14</f>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f>+raw!K14</f>
+        <f>+raw!M14</f>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f>+raw!L14</f>
+        <f>+raw!N14</f>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f>+raw!M14</f>
+        <f>+raw!O14</f>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f>+raw!N14</f>
+        <f>+raw!P14</f>
         <v>0</v>
       </c>
       <c r="AI14">
-        <f>+raw!O14</f>
+        <f>+raw!Q14</f>
         <v>0</v>
       </c>
       <c r="AK14">
-        <f>+raw!P14</f>
+        <f>+raw!R14</f>
         <v>0</v>
       </c>
       <c r="AM14">
-        <f>+raw!Q14</f>
+        <f>+raw!S14</f>
         <v>0</v>
       </c>
       <c r="AO14">
-        <f>+raw!R14</f>
+        <f>+raw!T14</f>
         <v>0</v>
       </c>
       <c r="AQ14">
-        <f>+raw!S14</f>
+        <f>+raw!U14</f>
         <v>0</v>
       </c>
       <c r="AS14">
-        <f>+raw!T14</f>
+        <f>+raw!V14</f>
         <v>0</v>
       </c>
       <c r="AU14">
-        <f>+raw!U14</f>
+        <f>+raw!W14</f>
         <v>0</v>
       </c>
       <c r="AW14">
-        <f>+raw!V14</f>
+        <f>+raw!X14</f>
         <v>0</v>
       </c>
       <c r="AY14">
-        <f>+raw!W14</f>
+        <f>+raw!Y14</f>
         <v>0</v>
       </c>
       <c r="BA14">
-        <f>+raw!X14</f>
+        <f>+raw!Z14</f>
         <v>0</v>
       </c>
       <c r="BC14">
-        <f>+raw!Y14</f>
+        <f>+raw!AA14</f>
         <v>0</v>
       </c>
       <c r="BE14">
-        <f>+raw!Z14</f>
+        <f>+raw!AB14</f>
         <v>0</v>
       </c>
       <c r="BG14">
-        <f>+raw!AA14</f>
+        <f>+raw!AC14</f>
         <v>0</v>
       </c>
       <c r="BI14">
-        <f>+raw!AB14</f>
+        <f>+raw!AD14</f>
         <v>0</v>
       </c>
       <c r="BK14">
-        <f>+raw!AC14</f>
+        <f>+raw!AE14</f>
         <v>0</v>
       </c>
       <c r="BM14">
-        <f>+raw!AD14</f>
+        <f>+raw!AF14</f>
         <v>0</v>
       </c>
       <c r="BO14">
-        <f>+raw!AE14</f>
+        <f>+raw!AG14</f>
         <v>0</v>
       </c>
     </row>
@@ -14077,111 +14161,111 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <f>+raw!E15</f>
+        <f>+raw!F15</f>
         <v>0</v>
       </c>
       <c r="R15">
-        <f>+raw!F15</f>
+        <f>+raw!H15</f>
         <v>0</v>
       </c>
       <c r="T15">
-        <f>+raw!G15</f>
+        <f>+raw!I15</f>
         <v>0</v>
       </c>
       <c r="V15">
-        <f>+raw!H15</f>
+        <f>+raw!J15</f>
         <v>0</v>
       </c>
       <c r="X15">
-        <f>+raw!I15</f>
+        <f>+raw!K15</f>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f>+raw!J15</f>
+        <f>+raw!L15</f>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f>+raw!K15</f>
+        <f>+raw!M15</f>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f>+raw!L15</f>
+        <f>+raw!N15</f>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f>+raw!M15</f>
+        <f>+raw!O15</f>
         <v>0</v>
       </c>
       <c r="AH15">
-        <f>+raw!N15</f>
+        <f>+raw!P15</f>
         <v>0</v>
       </c>
       <c r="AJ15">
-        <f>+raw!O15</f>
+        <f>+raw!Q15</f>
         <v>0</v>
       </c>
       <c r="AL15">
-        <f>+raw!P15</f>
+        <f>+raw!R15</f>
         <v>0</v>
       </c>
       <c r="AN15">
-        <f>+raw!Q15</f>
+        <f>+raw!S15</f>
         <v>0</v>
       </c>
       <c r="AP15">
-        <f>+raw!R15</f>
+        <f>+raw!T15</f>
         <v>0</v>
       </c>
       <c r="AR15">
-        <f>+raw!S15</f>
+        <f>+raw!U15</f>
         <v>0</v>
       </c>
       <c r="AT15">
-        <f>+raw!T15</f>
+        <f>+raw!V15</f>
         <v>0</v>
       </c>
       <c r="AV15">
-        <f>+raw!U15</f>
+        <f>+raw!W15</f>
         <v>0</v>
       </c>
       <c r="AX15">
-        <f>+raw!V15</f>
+        <f>+raw!X15</f>
         <v>0</v>
       </c>
       <c r="AZ15">
-        <f>+raw!W15</f>
+        <f>+raw!Y15</f>
         <v>0</v>
       </c>
       <c r="BB15">
-        <f>+raw!X15</f>
+        <f>+raw!Z15</f>
         <v>0</v>
       </c>
       <c r="BD15">
-        <f>+raw!Y15</f>
+        <f>+raw!AA15</f>
         <v>0</v>
       </c>
       <c r="BF15">
-        <f>+raw!Z15</f>
+        <f>+raw!AB15</f>
         <v>0</v>
       </c>
       <c r="BH15">
-        <f>+raw!AA15</f>
+        <f>+raw!AC15</f>
         <v>0</v>
       </c>
       <c r="BJ15">
-        <f>+raw!AB15</f>
+        <f>+raw!AD15</f>
         <v>0</v>
       </c>
       <c r="BL15">
-        <f>+raw!AC15</f>
+        <f>+raw!AE15</f>
         <v>0</v>
       </c>
       <c r="BN15">
-        <f>+raw!AD15</f>
+        <f>+raw!AF15</f>
         <v>0</v>
       </c>
       <c r="BP15">
-        <f>+raw!AE15</f>
+        <f>+raw!AG15</f>
         <v>0</v>
       </c>
     </row>
@@ -14191,111 +14275,111 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>+raw!E16</f>
+        <f>+raw!F16</f>
         <v>0</v>
       </c>
       <c r="S16">
-        <f>+raw!F16</f>
+        <f>+raw!H16</f>
         <v>0</v>
       </c>
       <c r="U16">
-        <f>+raw!G16</f>
+        <f>+raw!I16</f>
         <v>0</v>
       </c>
       <c r="W16">
-        <f>+raw!H16</f>
+        <f>+raw!J16</f>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f>+raw!I16</f>
+        <f>+raw!K16</f>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f>+raw!J16</f>
+        <f>+raw!L16</f>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f>+raw!K16</f>
+        <f>+raw!M16</f>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f>+raw!L16</f>
+        <f>+raw!N16</f>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f>+raw!M16</f>
+        <f>+raw!O16</f>
         <v>0</v>
       </c>
       <c r="AI16">
-        <f>+raw!N16</f>
+        <f>+raw!P16</f>
         <v>0</v>
       </c>
       <c r="AK16">
-        <f>+raw!O16</f>
+        <f>+raw!Q16</f>
         <v>0</v>
       </c>
       <c r="AM16">
-        <f>+raw!P16</f>
+        <f>+raw!R16</f>
         <v>0</v>
       </c>
       <c r="AO16">
-        <f>+raw!Q16</f>
+        <f>+raw!S16</f>
         <v>0</v>
       </c>
       <c r="AQ16">
-        <f>+raw!R16</f>
+        <f>+raw!T16</f>
         <v>0</v>
       </c>
       <c r="AS16">
-        <f>+raw!S16</f>
+        <f>+raw!U16</f>
         <v>0</v>
       </c>
       <c r="AU16">
-        <f>+raw!T16</f>
+        <f>+raw!V16</f>
         <v>0</v>
       </c>
       <c r="AW16">
-        <f>+raw!U16</f>
+        <f>+raw!W16</f>
         <v>0</v>
       </c>
       <c r="AY16">
-        <f>+raw!V16</f>
+        <f>+raw!X16</f>
         <v>0</v>
       </c>
       <c r="BA16">
-        <f>+raw!W16</f>
+        <f>+raw!Y16</f>
         <v>0</v>
       </c>
       <c r="BC16">
-        <f>+raw!X16</f>
+        <f>+raw!Z16</f>
         <v>0</v>
       </c>
       <c r="BE16">
-        <f>+raw!Y16</f>
+        <f>+raw!AA16</f>
         <v>0</v>
       </c>
       <c r="BG16">
-        <f>+raw!Z16</f>
+        <f>+raw!AB16</f>
         <v>0</v>
       </c>
       <c r="BI16">
-        <f>+raw!AA16</f>
+        <f>+raw!AC16</f>
         <v>0</v>
       </c>
       <c r="BK16">
-        <f>+raw!AB16</f>
+        <f>+raw!AD16</f>
         <v>0</v>
       </c>
       <c r="BM16">
-        <f>+raw!AC16</f>
+        <f>+raw!AE16</f>
         <v>0</v>
       </c>
       <c r="BO16">
-        <f>+raw!AD16</f>
+        <f>+raw!AF16</f>
         <v>0</v>
       </c>
       <c r="BQ16">
-        <f>+raw!AE16</f>
+        <f>+raw!AG16</f>
         <v>0</v>
       </c>
     </row>
@@ -14305,111 +14389,111 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <f>+raw!E17</f>
+        <f>+raw!F17</f>
         <v>0</v>
       </c>
       <c r="T17">
-        <f>+raw!F17</f>
+        <f>+raw!H17</f>
         <v>0</v>
       </c>
       <c r="V17">
-        <f>+raw!G17</f>
+        <f>+raw!I17</f>
         <v>0</v>
       </c>
       <c r="X17">
-        <f>+raw!H17</f>
+        <f>+raw!J17</f>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>+raw!I17</f>
+        <f>+raw!K17</f>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f>+raw!J17</f>
+        <f>+raw!L17</f>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f>+raw!K17</f>
+        <f>+raw!M17</f>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f>+raw!L17</f>
+        <f>+raw!N17</f>
         <v>0</v>
       </c>
       <c r="AH17">
-        <f>+raw!M17</f>
+        <f>+raw!O17</f>
         <v>0</v>
       </c>
       <c r="AJ17">
-        <f>+raw!N17</f>
+        <f>+raw!P17</f>
         <v>0</v>
       </c>
       <c r="AL17">
-        <f>+raw!O17</f>
+        <f>+raw!Q17</f>
         <v>0</v>
       </c>
       <c r="AN17">
-        <f>+raw!P17</f>
+        <f>+raw!R17</f>
         <v>0</v>
       </c>
       <c r="AP17">
-        <f>+raw!Q17</f>
+        <f>+raw!S17</f>
         <v>0</v>
       </c>
       <c r="AR17">
-        <f>+raw!R17</f>
+        <f>+raw!T17</f>
         <v>0</v>
       </c>
       <c r="AT17">
-        <f>+raw!S17</f>
+        <f>+raw!U17</f>
         <v>0</v>
       </c>
       <c r="AV17">
-        <f>+raw!T17</f>
+        <f>+raw!V17</f>
         <v>0</v>
       </c>
       <c r="AX17">
-        <f>+raw!U17</f>
+        <f>+raw!W17</f>
         <v>0</v>
       </c>
       <c r="AZ17">
-        <f>+raw!V17</f>
+        <f>+raw!X17</f>
         <v>0</v>
       </c>
       <c r="BB17">
-        <f>+raw!W17</f>
+        <f>+raw!Y17</f>
         <v>0</v>
       </c>
       <c r="BD17">
-        <f>+raw!X17</f>
+        <f>+raw!Z17</f>
         <v>0</v>
       </c>
       <c r="BF17">
-        <f>+raw!Y17</f>
+        <f>+raw!AA17</f>
         <v>0</v>
       </c>
       <c r="BH17">
-        <f>+raw!Z17</f>
+        <f>+raw!AB17</f>
         <v>0</v>
       </c>
       <c r="BJ17">
-        <f>+raw!AA17</f>
+        <f>+raw!AC17</f>
         <v>0</v>
       </c>
       <c r="BL17">
-        <f>+raw!AB17</f>
+        <f>+raw!AD17</f>
         <v>0</v>
       </c>
       <c r="BN17">
-        <f>+raw!AC17</f>
+        <f>+raw!AE17</f>
         <v>0</v>
       </c>
       <c r="BP17">
-        <f>+raw!AD17</f>
+        <f>+raw!AF17</f>
         <v>0</v>
       </c>
       <c r="BR17">
-        <f>+raw!AE17</f>
+        <f>+raw!AG17</f>
         <v>0</v>
       </c>
     </row>
@@ -14419,111 +14503,111 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <f>+raw!E18</f>
+        <f>+raw!F18</f>
         <v>0</v>
       </c>
       <c r="U18">
-        <f>+raw!F18</f>
+        <f>+raw!H18</f>
         <v>0</v>
       </c>
       <c r="W18">
-        <f>+raw!G18</f>
+        <f>+raw!I18</f>
         <v>0</v>
       </c>
       <c r="Y18">
-        <f>+raw!H18</f>
+        <f>+raw!J18</f>
         <v>0</v>
       </c>
       <c r="AA18">
-        <f>+raw!I18</f>
+        <f>+raw!K18</f>
         <v>0</v>
       </c>
       <c r="AC18">
-        <f>+raw!J18</f>
+        <f>+raw!L18</f>
         <v>0</v>
       </c>
       <c r="AE18">
-        <f>+raw!K18</f>
+        <f>+raw!M18</f>
         <v>0</v>
       </c>
       <c r="AG18">
-        <f>+raw!L18</f>
+        <f>+raw!N18</f>
         <v>0</v>
       </c>
       <c r="AI18">
-        <f>+raw!M18</f>
+        <f>+raw!O18</f>
         <v>0</v>
       </c>
       <c r="AK18">
-        <f>+raw!N18</f>
+        <f>+raw!P18</f>
         <v>0</v>
       </c>
       <c r="AM18">
-        <f>+raw!O18</f>
+        <f>+raw!Q18</f>
         <v>0</v>
       </c>
       <c r="AO18">
-        <f>+raw!P18</f>
+        <f>+raw!R18</f>
         <v>0</v>
       </c>
       <c r="AQ18">
-        <f>+raw!Q18</f>
+        <f>+raw!S18</f>
         <v>0</v>
       </c>
       <c r="AS18">
-        <f>+raw!R18</f>
+        <f>+raw!T18</f>
         <v>0</v>
       </c>
       <c r="AU18">
-        <f>+raw!S18</f>
+        <f>+raw!U18</f>
         <v>0</v>
       </c>
       <c r="AW18">
-        <f>+raw!T18</f>
+        <f>+raw!V18</f>
         <v>0</v>
       </c>
       <c r="AY18">
-        <f>+raw!U18</f>
+        <f>+raw!W18</f>
         <v>0</v>
       </c>
       <c r="BA18">
-        <f>+raw!V18</f>
+        <f>+raw!X18</f>
         <v>0</v>
       </c>
       <c r="BC18">
-        <f>+raw!W18</f>
+        <f>+raw!Y18</f>
         <v>0</v>
       </c>
       <c r="BE18">
-        <f>+raw!X18</f>
+        <f>+raw!Z18</f>
         <v>0</v>
       </c>
       <c r="BG18">
-        <f>+raw!Y18</f>
+        <f>+raw!AA18</f>
         <v>0</v>
       </c>
       <c r="BI18">
-        <f>+raw!Z18</f>
+        <f>+raw!AB18</f>
         <v>0</v>
       </c>
       <c r="BK18">
-        <f>+raw!AA18</f>
+        <f>+raw!AC18</f>
         <v>0</v>
       </c>
       <c r="BM18">
-        <f>+raw!AB18</f>
+        <f>+raw!AD18</f>
         <v>0</v>
       </c>
       <c r="BO18">
-        <f>+raw!AC18</f>
+        <f>+raw!AE18</f>
         <v>0</v>
       </c>
       <c r="BQ18">
-        <f>+raw!AD18</f>
+        <f>+raw!AF18</f>
         <v>0</v>
       </c>
       <c r="BS18">
-        <f>+raw!AE18</f>
+        <f>+raw!AG18</f>
         <v>0</v>
       </c>
     </row>
@@ -14533,111 +14617,111 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <f>+raw!E19</f>
+        <f>+raw!F19</f>
         <v>0</v>
       </c>
       <c r="V19">
-        <f>+raw!F19</f>
+        <f>+raw!H19</f>
         <v>0</v>
       </c>
       <c r="X19">
-        <f>+raw!G19</f>
+        <f>+raw!I19</f>
         <v>0</v>
       </c>
       <c r="Z19">
-        <f>+raw!H19</f>
+        <f>+raw!J19</f>
         <v>0</v>
       </c>
       <c r="AB19">
-        <f>+raw!I19</f>
+        <f>+raw!K19</f>
         <v>0</v>
       </c>
       <c r="AD19">
-        <f>+raw!J19</f>
+        <f>+raw!L19</f>
         <v>0</v>
       </c>
       <c r="AF19">
-        <f>+raw!K19</f>
+        <f>+raw!M19</f>
         <v>0</v>
       </c>
       <c r="AH19">
-        <f>+raw!L19</f>
+        <f>+raw!N19</f>
         <v>0</v>
       </c>
       <c r="AJ19">
-        <f>+raw!M19</f>
+        <f>+raw!O19</f>
         <v>0</v>
       </c>
       <c r="AL19">
-        <f>+raw!N19</f>
+        <f>+raw!P19</f>
         <v>0</v>
       </c>
       <c r="AN19">
-        <f>+raw!O19</f>
+        <f>+raw!Q19</f>
         <v>0</v>
       </c>
       <c r="AP19">
-        <f>+raw!P19</f>
+        <f>+raw!R19</f>
         <v>0</v>
       </c>
       <c r="AR19">
-        <f>+raw!Q19</f>
+        <f>+raw!S19</f>
         <v>0</v>
       </c>
       <c r="AT19">
-        <f>+raw!R19</f>
+        <f>+raw!T19</f>
         <v>0</v>
       </c>
       <c r="AV19">
-        <f>+raw!S19</f>
+        <f>+raw!U19</f>
         <v>0</v>
       </c>
       <c r="AX19">
-        <f>+raw!T19</f>
+        <f>+raw!V19</f>
         <v>0</v>
       </c>
       <c r="AZ19">
-        <f>+raw!U19</f>
+        <f>+raw!W19</f>
         <v>0</v>
       </c>
       <c r="BB19">
-        <f>+raw!V19</f>
+        <f>+raw!X19</f>
         <v>0</v>
       </c>
       <c r="BD19">
-        <f>+raw!W19</f>
+        <f>+raw!Y19</f>
         <v>0</v>
       </c>
       <c r="BF19">
-        <f>+raw!X19</f>
+        <f>+raw!Z19</f>
         <v>0</v>
       </c>
       <c r="BH19">
-        <f>+raw!Y19</f>
+        <f>+raw!AA19</f>
         <v>0</v>
       </c>
       <c r="BJ19">
-        <f>+raw!Z19</f>
+        <f>+raw!AB19</f>
         <v>0</v>
       </c>
       <c r="BL19">
-        <f>+raw!AA19</f>
+        <f>+raw!AC19</f>
         <v>0</v>
       </c>
       <c r="BN19">
-        <f>+raw!AB19</f>
+        <f>+raw!AD19</f>
         <v>0</v>
       </c>
       <c r="BP19">
-        <f>+raw!AC19</f>
+        <f>+raw!AE19</f>
         <v>0</v>
       </c>
       <c r="BR19">
-        <f>+raw!AD19</f>
+        <f>+raw!AF19</f>
         <v>0</v>
       </c>
       <c r="BT19">
-        <f>+raw!AE19</f>
+        <f>+raw!AG19</f>
         <v>0</v>
       </c>
     </row>
@@ -14647,111 +14731,111 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <f>+raw!E20</f>
+        <f>+raw!F20</f>
         <v>0</v>
       </c>
       <c r="W20">
-        <f>+raw!F20</f>
+        <f>+raw!H20</f>
         <v>0</v>
       </c>
       <c r="Y20">
-        <f>+raw!G20</f>
+        <f>+raw!I20</f>
         <v>0</v>
       </c>
       <c r="AA20">
-        <f>+raw!H20</f>
+        <f>+raw!J20</f>
         <v>0</v>
       </c>
       <c r="AC20">
-        <f>+raw!I20</f>
+        <f>+raw!K20</f>
         <v>0</v>
       </c>
       <c r="AE20">
-        <f>+raw!J20</f>
+        <f>+raw!L20</f>
         <v>0</v>
       </c>
       <c r="AG20">
-        <f>+raw!K20</f>
+        <f>+raw!M20</f>
         <v>0</v>
       </c>
       <c r="AI20">
-        <f>+raw!L20</f>
+        <f>+raw!N20</f>
         <v>0</v>
       </c>
       <c r="AK20">
-        <f>+raw!M20</f>
+        <f>+raw!O20</f>
         <v>0</v>
       </c>
       <c r="AM20">
-        <f>+raw!N20</f>
+        <f>+raw!P20</f>
         <v>0</v>
       </c>
       <c r="AO20">
-        <f>+raw!O20</f>
+        <f>+raw!Q20</f>
         <v>0</v>
       </c>
       <c r="AQ20">
-        <f>+raw!P20</f>
+        <f>+raw!R20</f>
         <v>0</v>
       </c>
       <c r="AS20">
-        <f>+raw!Q20</f>
+        <f>+raw!S20</f>
         <v>0</v>
       </c>
       <c r="AU20">
-        <f>+raw!R20</f>
+        <f>+raw!T20</f>
         <v>0</v>
       </c>
       <c r="AW20">
-        <f>+raw!S20</f>
+        <f>+raw!U20</f>
         <v>0</v>
       </c>
       <c r="AY20">
-        <f>+raw!T20</f>
+        <f>+raw!V20</f>
         <v>0</v>
       </c>
       <c r="BA20">
-        <f>+raw!U20</f>
+        <f>+raw!W20</f>
         <v>0</v>
       </c>
       <c r="BC20">
-        <f>+raw!V20</f>
+        <f>+raw!X20</f>
         <v>0</v>
       </c>
       <c r="BE20">
-        <f>+raw!W20</f>
+        <f>+raw!Y20</f>
         <v>0</v>
       </c>
       <c r="BG20">
-        <f>+raw!X20</f>
+        <f>+raw!Z20</f>
         <v>0</v>
       </c>
       <c r="BI20">
-        <f>+raw!Y20</f>
+        <f>+raw!AA20</f>
         <v>0</v>
       </c>
       <c r="BK20">
-        <f>+raw!Z20</f>
+        <f>+raw!AB20</f>
         <v>0</v>
       </c>
       <c r="BM20">
-        <f>+raw!AA20</f>
+        <f>+raw!AC20</f>
         <v>0</v>
       </c>
       <c r="BO20">
-        <f>+raw!AB20</f>
+        <f>+raw!AD20</f>
         <v>0</v>
       </c>
       <c r="BQ20">
-        <f>+raw!AC20</f>
+        <f>+raw!AE20</f>
         <v>0</v>
       </c>
       <c r="BS20">
-        <f>+raw!AD20</f>
+        <f>+raw!AF20</f>
         <v>0</v>
       </c>
       <c r="BU20">
-        <f>+raw!AE20</f>
+        <f>+raw!AG20</f>
         <v>0</v>
       </c>
     </row>
@@ -14761,111 +14845,111 @@
         <v>0</v>
       </c>
       <c r="V21">
-        <f>+raw!E21</f>
+        <f>+raw!F21</f>
         <v>0</v>
       </c>
       <c r="X21">
-        <f>+raw!F21</f>
+        <f>+raw!H21</f>
         <v>0</v>
       </c>
       <c r="Z21">
-        <f>+raw!G21</f>
+        <f>+raw!I21</f>
         <v>0</v>
       </c>
       <c r="AB21">
-        <f>+raw!H21</f>
+        <f>+raw!J21</f>
         <v>0</v>
       </c>
       <c r="AD21">
-        <f>+raw!I21</f>
+        <f>+raw!K21</f>
         <v>0</v>
       </c>
       <c r="AF21">
-        <f>+raw!J21</f>
+        <f>+raw!L21</f>
         <v>0</v>
       </c>
       <c r="AH21">
-        <f>+raw!K21</f>
+        <f>+raw!M21</f>
         <v>0</v>
       </c>
       <c r="AJ21">
-        <f>+raw!L21</f>
+        <f>+raw!N21</f>
         <v>0</v>
       </c>
       <c r="AL21">
-        <f>+raw!M21</f>
+        <f>+raw!O21</f>
         <v>0</v>
       </c>
       <c r="AN21">
-        <f>+raw!N21</f>
+        <f>+raw!P21</f>
         <v>0</v>
       </c>
       <c r="AP21">
-        <f>+raw!O21</f>
+        <f>+raw!Q21</f>
         <v>0</v>
       </c>
       <c r="AR21">
-        <f>+raw!P21</f>
+        <f>+raw!R21</f>
         <v>0</v>
       </c>
       <c r="AT21">
-        <f>+raw!Q21</f>
+        <f>+raw!S21</f>
         <v>0</v>
       </c>
       <c r="AV21">
-        <f>+raw!R21</f>
+        <f>+raw!T21</f>
         <v>0</v>
       </c>
       <c r="AX21">
-        <f>+raw!S21</f>
+        <f>+raw!U21</f>
         <v>0</v>
       </c>
       <c r="AZ21">
-        <f>+raw!T21</f>
+        <f>+raw!V21</f>
         <v>0</v>
       </c>
       <c r="BB21">
-        <f>+raw!U21</f>
-        <v>0</v>
+        <f>+raw!W21</f>
+        <v>1</v>
       </c>
       <c r="BD21">
-        <f>+raw!V21</f>
+        <f>+raw!X21</f>
         <v>0</v>
       </c>
       <c r="BF21">
-        <f>+raw!W21</f>
+        <f>+raw!Y21</f>
         <v>0</v>
       </c>
       <c r="BH21">
-        <f>+raw!X21</f>
+        <f>+raw!Z21</f>
         <v>0</v>
       </c>
       <c r="BJ21">
-        <f>+raw!Y21</f>
+        <f>+raw!AA21</f>
         <v>0</v>
       </c>
       <c r="BL21">
-        <f>+raw!Z21</f>
+        <f>+raw!AB21</f>
         <v>0</v>
       </c>
       <c r="BN21">
-        <f>+raw!AA21</f>
+        <f>+raw!AC21</f>
         <v>0</v>
       </c>
       <c r="BP21">
-        <f>+raw!AB21</f>
+        <f>+raw!AD21</f>
         <v>0</v>
       </c>
       <c r="BR21">
-        <f>+raw!AC21</f>
+        <f>+raw!AE21</f>
         <v>0</v>
       </c>
       <c r="BT21">
-        <f>+raw!AD21</f>
+        <f>+raw!AF21</f>
         <v>0</v>
       </c>
       <c r="BV21">
-        <f>+raw!AE21</f>
+        <f>+raw!AG21</f>
         <v>0</v>
       </c>
     </row>
@@ -14875,111 +14959,111 @@
         <v>0</v>
       </c>
       <c r="W22">
-        <f>+raw!E22</f>
+        <f>+raw!F22</f>
         <v>0</v>
       </c>
       <c r="Y22">
-        <f>+raw!F22</f>
+        <f>+raw!H22</f>
         <v>0</v>
       </c>
       <c r="AA22">
-        <f>+raw!G22</f>
+        <f>+raw!I22</f>
         <v>0</v>
       </c>
       <c r="AC22">
-        <f>+raw!H22</f>
+        <f>+raw!J22</f>
         <v>0</v>
       </c>
       <c r="AE22">
-        <f>+raw!I22</f>
+        <f>+raw!K22</f>
         <v>0</v>
       </c>
       <c r="AG22">
-        <f>+raw!J22</f>
+        <f>+raw!L22</f>
         <v>0</v>
       </c>
       <c r="AI22">
-        <f>+raw!K22</f>
+        <f>+raw!M22</f>
         <v>0</v>
       </c>
       <c r="AK22">
-        <f>+raw!L22</f>
+        <f>+raw!N22</f>
         <v>0</v>
       </c>
       <c r="AM22">
-        <f>+raw!M22</f>
+        <f>+raw!O22</f>
         <v>0</v>
       </c>
       <c r="AO22">
-        <f>+raw!N22</f>
+        <f>+raw!P22</f>
         <v>0</v>
       </c>
       <c r="AQ22">
-        <f>+raw!O22</f>
+        <f>+raw!Q22</f>
         <v>0</v>
       </c>
       <c r="AS22">
-        <f>+raw!P22</f>
+        <f>+raw!R22</f>
         <v>0</v>
       </c>
       <c r="AU22">
-        <f>+raw!Q22</f>
+        <f>+raw!S22</f>
         <v>0</v>
       </c>
       <c r="AW22">
-        <f>+raw!R22</f>
+        <f>+raw!T22</f>
         <v>0</v>
       </c>
       <c r="AY22">
-        <f>+raw!S22</f>
+        <f>+raw!U22</f>
         <v>0</v>
       </c>
       <c r="BA22">
-        <f>+raw!T22</f>
+        <f>+raw!V22</f>
         <v>0</v>
       </c>
       <c r="BC22">
-        <f>+raw!U22</f>
-        <v>0</v>
+        <f>+raw!W22</f>
+        <v>1</v>
       </c>
       <c r="BE22">
-        <f>+raw!V22</f>
+        <f>+raw!X22</f>
         <v>0</v>
       </c>
       <c r="BG22">
-        <f>+raw!W22</f>
+        <f>+raw!Y22</f>
         <v>0</v>
       </c>
       <c r="BI22">
-        <f>+raw!X22</f>
+        <f>+raw!Z22</f>
         <v>0</v>
       </c>
       <c r="BK22">
-        <f>+raw!Y22</f>
+        <f>+raw!AA22</f>
         <v>0</v>
       </c>
       <c r="BM22">
-        <f>+raw!Z22</f>
+        <f>+raw!AB22</f>
         <v>0</v>
       </c>
       <c r="BO22">
-        <f>+raw!AA22</f>
+        <f>+raw!AC22</f>
         <v>0</v>
       </c>
       <c r="BQ22">
-        <f>+raw!AB22</f>
+        <f>+raw!AD22</f>
         <v>0</v>
       </c>
       <c r="BS22">
-        <f>+raw!AC22</f>
+        <f>+raw!AE22</f>
         <v>0</v>
       </c>
       <c r="BU22">
-        <f>+raw!AD22</f>
+        <f>+raw!AF22</f>
         <v>0</v>
       </c>
       <c r="BW22">
-        <f>+raw!AE22</f>
+        <f>+raw!AG22</f>
         <v>0</v>
       </c>
     </row>
@@ -14989,111 +15073,111 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <f>+raw!E23</f>
+        <f>+raw!F23</f>
         <v>0</v>
       </c>
       <c r="Z23">
-        <f>+raw!F23</f>
+        <f>+raw!H23</f>
         <v>0</v>
       </c>
       <c r="AB23">
-        <f>+raw!G23</f>
+        <f>+raw!I23</f>
         <v>0</v>
       </c>
       <c r="AD23">
-        <f>+raw!H23</f>
+        <f>+raw!J23</f>
         <v>0</v>
       </c>
       <c r="AF23">
-        <f>+raw!I23</f>
+        <f>+raw!K23</f>
         <v>0</v>
       </c>
       <c r="AH23">
-        <f>+raw!J23</f>
+        <f>+raw!L23</f>
         <v>0</v>
       </c>
       <c r="AJ23">
-        <f>+raw!K23</f>
+        <f>+raw!M23</f>
         <v>0</v>
       </c>
       <c r="AL23">
-        <f>+raw!L23</f>
+        <f>+raw!N23</f>
         <v>0</v>
       </c>
       <c r="AN23">
-        <f>+raw!M23</f>
+        <f>+raw!O23</f>
         <v>0</v>
       </c>
       <c r="AP23">
-        <f>+raw!N23</f>
+        <f>+raw!P23</f>
         <v>0</v>
       </c>
       <c r="AR23">
-        <f>+raw!O23</f>
+        <f>+raw!Q23</f>
         <v>0</v>
       </c>
       <c r="AT23">
-        <f>+raw!P23</f>
+        <f>+raw!R23</f>
         <v>0</v>
       </c>
       <c r="AV23">
-        <f>+raw!Q23</f>
+        <f>+raw!S23</f>
         <v>0</v>
       </c>
       <c r="AX23">
-        <f>+raw!R23</f>
+        <f>+raw!T23</f>
         <v>0</v>
       </c>
       <c r="AZ23">
-        <f>+raw!S23</f>
+        <f>+raw!U23</f>
         <v>0</v>
       </c>
       <c r="BB23">
-        <f>+raw!T23</f>
+        <f>+raw!V23</f>
         <v>1</v>
       </c>
       <c r="BD23">
-        <f>+raw!U23</f>
-        <v>0</v>
+        <f>+raw!W23</f>
+        <v>1</v>
       </c>
       <c r="BF23">
-        <f>+raw!V23</f>
+        <f>+raw!X23</f>
         <v>0</v>
       </c>
       <c r="BH23">
-        <f>+raw!W23</f>
+        <f>+raw!Y23</f>
         <v>0</v>
       </c>
       <c r="BJ23">
-        <f>+raw!X23</f>
+        <f>+raw!Z23</f>
         <v>0</v>
       </c>
       <c r="BL23">
-        <f>+raw!Y23</f>
+        <f>+raw!AA23</f>
         <v>0</v>
       </c>
       <c r="BN23">
-        <f>+raw!Z23</f>
+        <f>+raw!AB23</f>
         <v>0</v>
       </c>
       <c r="BP23">
-        <f>+raw!AA23</f>
+        <f>+raw!AC23</f>
         <v>0</v>
       </c>
       <c r="BR23">
-        <f>+raw!AB23</f>
+        <f>+raw!AD23</f>
         <v>0</v>
       </c>
       <c r="BT23">
-        <f>+raw!AC23</f>
+        <f>+raw!AE23</f>
         <v>0</v>
       </c>
       <c r="BV23">
-        <f>+raw!AD23</f>
+        <f>+raw!AF23</f>
         <v>0</v>
       </c>
       <c r="BX23">
-        <f>+raw!AE23</f>
+        <f>+raw!AG23</f>
         <v>0</v>
       </c>
     </row>
@@ -15103,111 +15187,111 @@
         <v>0</v>
       </c>
       <c r="Y24">
-        <f>+raw!E24</f>
+        <f>+raw!F24</f>
         <v>0</v>
       </c>
       <c r="AA24">
-        <f>+raw!F24</f>
+        <f>+raw!H24</f>
         <v>0</v>
       </c>
       <c r="AC24">
-        <f>+raw!G24</f>
+        <f>+raw!I24</f>
         <v>0</v>
       </c>
       <c r="AE24">
-        <f>+raw!H24</f>
+        <f>+raw!J24</f>
         <v>0</v>
       </c>
       <c r="AG24">
-        <f>+raw!I24</f>
+        <f>+raw!K24</f>
         <v>0</v>
       </c>
       <c r="AI24">
-        <f>+raw!J24</f>
+        <f>+raw!L24</f>
         <v>0</v>
       </c>
       <c r="AK24">
-        <f>+raw!K24</f>
+        <f>+raw!M24</f>
         <v>0</v>
       </c>
       <c r="AM24">
-        <f>+raw!L24</f>
+        <f>+raw!N24</f>
         <v>0</v>
       </c>
       <c r="AO24">
-        <f>+raw!M24</f>
+        <f>+raw!O24</f>
         <v>0</v>
       </c>
       <c r="AQ24">
-        <f>+raw!N24</f>
+        <f>+raw!P24</f>
         <v>0</v>
       </c>
       <c r="AS24">
-        <f>+raw!O24</f>
+        <f>+raw!Q24</f>
         <v>0</v>
       </c>
       <c r="AU24">
-        <f>+raw!P24</f>
+        <f>+raw!R24</f>
         <v>0</v>
       </c>
       <c r="AW24">
-        <f>+raw!Q24</f>
+        <f>+raw!S24</f>
         <v>0</v>
       </c>
       <c r="AY24">
-        <f>+raw!R24</f>
+        <f>+raw!T24</f>
         <v>0</v>
       </c>
       <c r="BA24">
-        <f>+raw!S24</f>
+        <f>+raw!U24</f>
         <v>0</v>
       </c>
       <c r="BC24">
-        <f>+raw!T24</f>
+        <f>+raw!V24</f>
         <v>1</v>
       </c>
       <c r="BE24">
-        <f>+raw!U24</f>
+        <f>+raw!W24</f>
         <v>0</v>
       </c>
       <c r="BG24">
-        <f>+raw!V24</f>
+        <f>+raw!X24</f>
         <v>0</v>
       </c>
       <c r="BI24">
-        <f>+raw!W24</f>
+        <f>+raw!Y24</f>
         <v>0</v>
       </c>
       <c r="BK24">
-        <f>+raw!X24</f>
+        <f>+raw!Z24</f>
         <v>0</v>
       </c>
       <c r="BM24">
-        <f>+raw!Y24</f>
+        <f>+raw!AA24</f>
         <v>0</v>
       </c>
       <c r="BO24">
-        <f>+raw!Z24</f>
+        <f>+raw!AB24</f>
         <v>0</v>
       </c>
       <c r="BQ24">
-        <f>+raw!AA24</f>
+        <f>+raw!AC24</f>
         <v>0</v>
       </c>
       <c r="BS24">
-        <f>+raw!AB24</f>
+        <f>+raw!AD24</f>
         <v>0</v>
       </c>
       <c r="BU24">
-        <f>+raw!AC24</f>
+        <f>+raw!AE24</f>
         <v>0</v>
       </c>
       <c r="BW24">
-        <f>+raw!AD24</f>
+        <f>+raw!AF24</f>
         <v>0</v>
       </c>
       <c r="BY24">
-        <f>+raw!AE24</f>
+        <f>+raw!AG24</f>
         <v>0</v>
       </c>
     </row>
@@ -15217,111 +15301,111 @@
         <v>0</v>
       </c>
       <c r="Z25">
-        <f>+raw!E25</f>
+        <f>+raw!F25</f>
         <v>0</v>
       </c>
       <c r="AB25">
-        <f>+raw!F25</f>
+        <f>+raw!H25</f>
         <v>0</v>
       </c>
       <c r="AD25">
-        <f>+raw!G25</f>
+        <f>+raw!I25</f>
         <v>0</v>
       </c>
       <c r="AF25">
-        <f>+raw!H25</f>
+        <f>+raw!J25</f>
         <v>0</v>
       </c>
       <c r="AH25">
-        <f>+raw!I25</f>
+        <f>+raw!K25</f>
         <v>0</v>
       </c>
       <c r="AJ25">
-        <f>+raw!J25</f>
+        <f>+raw!L25</f>
         <v>0</v>
       </c>
       <c r="AL25">
-        <f>+raw!K25</f>
+        <f>+raw!M25</f>
         <v>0</v>
       </c>
       <c r="AN25">
-        <f>+raw!L25</f>
+        <f>+raw!N25</f>
         <v>0</v>
       </c>
       <c r="AP25">
-        <f>+raw!M25</f>
+        <f>+raw!O25</f>
         <v>0</v>
       </c>
       <c r="AR25">
-        <f>+raw!N25</f>
+        <f>+raw!P25</f>
         <v>0</v>
       </c>
       <c r="AT25">
-        <f>+raw!O25</f>
+        <f>+raw!Q25</f>
         <v>0</v>
       </c>
       <c r="AV25">
-        <f>+raw!P25</f>
+        <f>+raw!R25</f>
         <v>0</v>
       </c>
       <c r="AX25">
-        <f>+raw!Q25</f>
+        <f>+raw!S25</f>
         <v>0</v>
       </c>
       <c r="AZ25">
-        <f>+raw!R25</f>
+        <f>+raw!T25</f>
         <v>0</v>
       </c>
       <c r="BB25">
-        <f>+raw!S25</f>
+        <f>+raw!U25</f>
         <v>1</v>
       </c>
       <c r="BD25">
-        <f>+raw!T25</f>
+        <f>+raw!V25</f>
         <v>1</v>
       </c>
       <c r="BF25">
-        <f>+raw!U25</f>
+        <f>+raw!W25</f>
         <v>0</v>
       </c>
       <c r="BH25">
-        <f>+raw!V25</f>
+        <f>+raw!X25</f>
         <v>0</v>
       </c>
       <c r="BJ25">
-        <f>+raw!W25</f>
+        <f>+raw!Y25</f>
         <v>0</v>
       </c>
       <c r="BL25">
-        <f>+raw!X25</f>
+        <f>+raw!Z25</f>
         <v>0</v>
       </c>
       <c r="BN25">
-        <f>+raw!Y25</f>
+        <f>+raw!AA25</f>
         <v>0</v>
       </c>
       <c r="BP25">
-        <f>+raw!Z25</f>
+        <f>+raw!AB25</f>
         <v>0</v>
       </c>
       <c r="BR25">
-        <f>+raw!AA25</f>
+        <f>+raw!AC25</f>
         <v>0</v>
       </c>
       <c r="BT25">
-        <f>+raw!AB25</f>
+        <f>+raw!AD25</f>
         <v>0</v>
       </c>
       <c r="BV25">
-        <f>+raw!AC25</f>
+        <f>+raw!AE25</f>
         <v>0</v>
       </c>
       <c r="BX25">
-        <f>+raw!AD25</f>
+        <f>+raw!AF25</f>
         <v>0</v>
       </c>
       <c r="BZ25">
-        <f>+raw!AE25</f>
+        <f>+raw!AG25</f>
         <v>0</v>
       </c>
     </row>
@@ -15331,111 +15415,111 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <f>+raw!E26</f>
+        <f>+raw!F26</f>
         <v>0</v>
       </c>
       <c r="AC26">
-        <f>+raw!F26</f>
+        <f>+raw!H26</f>
         <v>0</v>
       </c>
       <c r="AE26">
-        <f>+raw!G26</f>
+        <f>+raw!I26</f>
         <v>0</v>
       </c>
       <c r="AG26">
-        <f>+raw!H26</f>
+        <f>+raw!J26</f>
         <v>0</v>
       </c>
       <c r="AI26">
-        <f>+raw!I26</f>
+        <f>+raw!K26</f>
         <v>0</v>
       </c>
       <c r="AK26">
-        <f>+raw!J26</f>
+        <f>+raw!L26</f>
         <v>0</v>
       </c>
       <c r="AM26">
-        <f>+raw!K26</f>
+        <f>+raw!M26</f>
         <v>0</v>
       </c>
       <c r="AO26">
-        <f>+raw!L26</f>
+        <f>+raw!N26</f>
         <v>0</v>
       </c>
       <c r="AQ26">
-        <f>+raw!M26</f>
+        <f>+raw!O26</f>
         <v>0</v>
       </c>
       <c r="AS26">
-        <f>+raw!N26</f>
+        <f>+raw!P26</f>
         <v>0</v>
       </c>
       <c r="AU26">
-        <f>+raw!O26</f>
+        <f>+raw!Q26</f>
         <v>0</v>
       </c>
       <c r="AW26">
-        <f>+raw!P26</f>
+        <f>+raw!R26</f>
         <v>0</v>
       </c>
       <c r="AY26">
-        <f>+raw!Q26</f>
+        <f>+raw!S26</f>
         <v>0</v>
       </c>
       <c r="BA26">
-        <f>+raw!R26</f>
+        <f>+raw!T26</f>
         <v>0</v>
       </c>
       <c r="BC26">
-        <f>+raw!S26</f>
+        <f>+raw!U26</f>
         <v>1</v>
       </c>
       <c r="BE26">
-        <f>+raw!T26</f>
+        <f>+raw!V26</f>
         <v>0</v>
       </c>
       <c r="BG26">
-        <f>+raw!U26</f>
+        <f>+raw!W26</f>
         <v>0</v>
       </c>
       <c r="BI26">
-        <f>+raw!V26</f>
+        <f>+raw!X26</f>
         <v>0</v>
       </c>
       <c r="BK26">
-        <f>+raw!W26</f>
+        <f>+raw!Y26</f>
         <v>0</v>
       </c>
       <c r="BM26">
-        <f>+raw!X26</f>
+        <f>+raw!Z26</f>
         <v>0</v>
       </c>
       <c r="BO26">
-        <f>+raw!Y26</f>
+        <f>+raw!AA26</f>
         <v>0</v>
       </c>
       <c r="BQ26">
-        <f>+raw!Z26</f>
+        <f>+raw!AB26</f>
         <v>0</v>
       </c>
       <c r="BS26">
-        <f>+raw!AA26</f>
+        <f>+raw!AC26</f>
         <v>0</v>
       </c>
       <c r="BU26">
-        <f>+raw!AB26</f>
+        <f>+raw!AD26</f>
         <v>0</v>
       </c>
       <c r="BW26">
-        <f>+raw!AC26</f>
+        <f>+raw!AE26</f>
         <v>0</v>
       </c>
       <c r="BY26">
-        <f>+raw!AD26</f>
+        <f>+raw!AF26</f>
         <v>0</v>
       </c>
       <c r="CA26">
-        <f>+raw!AE26</f>
+        <f>+raw!AG26</f>
         <v>0</v>
       </c>
     </row>
@@ -15445,111 +15529,111 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <f>+raw!E27</f>
+        <f>+raw!F27</f>
         <v>0</v>
       </c>
       <c r="AD27">
-        <f>+raw!F27</f>
+        <f>+raw!H27</f>
         <v>0</v>
       </c>
       <c r="AF27">
-        <f>+raw!G27</f>
+        <f>+raw!I27</f>
         <v>0</v>
       </c>
       <c r="AH27">
-        <f>+raw!H27</f>
+        <f>+raw!J27</f>
         <v>0</v>
       </c>
       <c r="AJ27">
-        <f>+raw!I27</f>
+        <f>+raw!K27</f>
         <v>0</v>
       </c>
       <c r="AL27">
-        <f>+raw!J27</f>
+        <f>+raw!L27</f>
         <v>0</v>
       </c>
       <c r="AN27">
-        <f>+raw!K27</f>
+        <f>+raw!M27</f>
         <v>0</v>
       </c>
       <c r="AP27">
-        <f>+raw!L27</f>
+        <f>+raw!N27</f>
         <v>0</v>
       </c>
       <c r="AR27">
-        <f>+raw!M27</f>
+        <f>+raw!O27</f>
         <v>0</v>
       </c>
       <c r="AT27">
-        <f>+raw!N27</f>
+        <f>+raw!P27</f>
         <v>0</v>
       </c>
       <c r="AV27">
-        <f>+raw!O27</f>
+        <f>+raw!Q27</f>
         <v>0</v>
       </c>
       <c r="AX27">
-        <f>+raw!P27</f>
+        <f>+raw!R27</f>
         <v>0</v>
       </c>
       <c r="AZ27">
-        <f>+raw!Q27</f>
+        <f>+raw!S27</f>
         <v>0</v>
       </c>
       <c r="BB27">
-        <f>+raw!R27</f>
+        <f>+raw!T27</f>
         <v>1</v>
       </c>
       <c r="BD27">
-        <f>+raw!S27</f>
+        <f>+raw!U27</f>
         <v>1</v>
       </c>
       <c r="BF27">
-        <f>+raw!T27</f>
+        <f>+raw!V27</f>
         <v>0</v>
       </c>
       <c r="BH27">
-        <f>+raw!U27</f>
+        <f>+raw!W27</f>
         <v>0</v>
       </c>
       <c r="BJ27">
-        <f>+raw!V27</f>
+        <f>+raw!X27</f>
         <v>0</v>
       </c>
       <c r="BL27">
-        <f>+raw!W27</f>
+        <f>+raw!Y27</f>
         <v>0</v>
       </c>
       <c r="BN27">
-        <f>+raw!X27</f>
+        <f>+raw!Z27</f>
         <v>0</v>
       </c>
       <c r="BP27">
-        <f>+raw!Y27</f>
+        <f>+raw!AA27</f>
         <v>0</v>
       </c>
       <c r="BR27">
-        <f>+raw!Z27</f>
+        <f>+raw!AB27</f>
         <v>0</v>
       </c>
       <c r="BT27">
-        <f>+raw!AA27</f>
+        <f>+raw!AC27</f>
         <v>0</v>
       </c>
       <c r="BV27">
-        <f>+raw!AB27</f>
+        <f>+raw!AD27</f>
         <v>0</v>
       </c>
       <c r="BX27">
-        <f>+raw!AC27</f>
+        <f>+raw!AE27</f>
         <v>0</v>
       </c>
       <c r="BZ27">
-        <f>+raw!AD27</f>
+        <f>+raw!AF27</f>
         <v>0</v>
       </c>
       <c r="CB27">
-        <f>+raw!AE27</f>
+        <f>+raw!AG27</f>
         <v>0</v>
       </c>
     </row>
@@ -15559,111 +15643,111 @@
         <v>0</v>
       </c>
       <c r="AC28">
-        <f>+raw!E28</f>
+        <f>+raw!F28</f>
         <v>0</v>
       </c>
       <c r="AE28">
-        <f>+raw!F28</f>
+        <f>+raw!H28</f>
         <v>0</v>
       </c>
       <c r="AG28">
-        <f>+raw!G28</f>
+        <f>+raw!I28</f>
         <v>0</v>
       </c>
       <c r="AI28">
-        <f>+raw!H28</f>
+        <f>+raw!J28</f>
         <v>0</v>
       </c>
       <c r="AK28">
-        <f>+raw!I28</f>
+        <f>+raw!K28</f>
         <v>0</v>
       </c>
       <c r="AM28">
-        <f>+raw!J28</f>
+        <f>+raw!L28</f>
         <v>0</v>
       </c>
       <c r="AO28">
-        <f>+raw!K28</f>
+        <f>+raw!M28</f>
         <v>0</v>
       </c>
       <c r="AQ28">
-        <f>+raw!L28</f>
+        <f>+raw!N28</f>
         <v>0</v>
       </c>
       <c r="AS28">
-        <f>+raw!M28</f>
+        <f>+raw!O28</f>
         <v>0</v>
       </c>
       <c r="AU28">
-        <f>+raw!N28</f>
+        <f>+raw!P28</f>
         <v>0</v>
       </c>
       <c r="AW28">
-        <f>+raw!O28</f>
+        <f>+raw!Q28</f>
         <v>0</v>
       </c>
       <c r="AY28">
-        <f>+raw!P28</f>
+        <f>+raw!R28</f>
         <v>0</v>
       </c>
       <c r="BA28">
-        <f>+raw!Q28</f>
+        <f>+raw!S28</f>
         <v>0</v>
       </c>
       <c r="BC28">
-        <f>+raw!R28</f>
+        <f>+raw!T28</f>
         <v>1</v>
       </c>
       <c r="BE28">
-        <f>+raw!S28</f>
+        <f>+raw!U28</f>
         <v>0</v>
       </c>
       <c r="BG28">
-        <f>+raw!T28</f>
+        <f>+raw!V28</f>
         <v>0</v>
       </c>
       <c r="BI28">
-        <f>+raw!U28</f>
+        <f>+raw!W28</f>
         <v>0</v>
       </c>
       <c r="BK28">
-        <f>+raw!V28</f>
+        <f>+raw!X28</f>
         <v>0</v>
       </c>
       <c r="BM28">
-        <f>+raw!W28</f>
+        <f>+raw!Y28</f>
         <v>0</v>
       </c>
       <c r="BO28">
-        <f>+raw!X28</f>
+        <f>+raw!Z28</f>
         <v>0</v>
       </c>
       <c r="BQ28">
-        <f>+raw!Y28</f>
+        <f>+raw!AA28</f>
         <v>0</v>
       </c>
       <c r="BS28">
-        <f>+raw!Z28</f>
+        <f>+raw!AB28</f>
         <v>0</v>
       </c>
       <c r="BU28">
-        <f>+raw!AA28</f>
+        <f>+raw!AC28</f>
         <v>0</v>
       </c>
       <c r="BW28">
-        <f>+raw!AB28</f>
+        <f>+raw!AD28</f>
         <v>0</v>
       </c>
       <c r="BY28">
-        <f>+raw!AC28</f>
+        <f>+raw!AE28</f>
         <v>0</v>
       </c>
       <c r="CA28">
-        <f>+raw!AD28</f>
+        <f>+raw!AF28</f>
         <v>0</v>
       </c>
       <c r="CC28">
-        <f>+raw!AE28</f>
+        <f>+raw!AG28</f>
         <v>0</v>
       </c>
     </row>
@@ -15673,111 +15757,111 @@
         <v>0</v>
       </c>
       <c r="AD29">
-        <f>+raw!E29</f>
+        <f>+raw!F29</f>
         <v>0</v>
       </c>
       <c r="AF29">
-        <f>+raw!F29</f>
+        <f>+raw!H29</f>
         <v>0</v>
       </c>
       <c r="AH29">
-        <f>+raw!G29</f>
+        <f>+raw!I29</f>
         <v>0</v>
       </c>
       <c r="AJ29">
-        <f>+raw!H29</f>
+        <f>+raw!J29</f>
         <v>0</v>
       </c>
       <c r="AL29">
-        <f>+raw!I29</f>
+        <f>+raw!K29</f>
         <v>0</v>
       </c>
       <c r="AN29">
-        <f>+raw!J29</f>
+        <f>+raw!L29</f>
         <v>0</v>
       </c>
       <c r="AP29">
-        <f>+raw!K29</f>
+        <f>+raw!M29</f>
         <v>0</v>
       </c>
       <c r="AR29">
-        <f>+raw!L29</f>
+        <f>+raw!N29</f>
         <v>0</v>
       </c>
       <c r="AT29">
-        <f>+raw!M29</f>
+        <f>+raw!O29</f>
         <v>0</v>
       </c>
       <c r="AV29">
-        <f>+raw!N29</f>
+        <f>+raw!P29</f>
         <v>0</v>
       </c>
       <c r="AX29">
-        <f>+raw!O29</f>
+        <f>+raw!Q29</f>
         <v>0</v>
       </c>
       <c r="AZ29">
-        <f>+raw!P29</f>
+        <f>+raw!R29</f>
         <v>0</v>
       </c>
       <c r="BB29">
-        <f>+raw!Q29</f>
+        <f>+raw!S29</f>
         <v>1</v>
       </c>
       <c r="BD29">
-        <f>+raw!R29</f>
+        <f>+raw!T29</f>
         <v>1</v>
       </c>
       <c r="BF29">
-        <f>+raw!S29</f>
+        <f>+raw!U29</f>
         <v>0</v>
       </c>
       <c r="BH29">
-        <f>+raw!T29</f>
+        <f>+raw!V29</f>
         <v>0</v>
       </c>
       <c r="BJ29">
-        <f>+raw!U29</f>
+        <f>+raw!W29</f>
         <v>0</v>
       </c>
       <c r="BL29">
-        <f>+raw!V29</f>
+        <f>+raw!X29</f>
         <v>0</v>
       </c>
       <c r="BN29">
-        <f>+raw!W29</f>
+        <f>+raw!Y29</f>
         <v>0</v>
       </c>
       <c r="BP29">
-        <f>+raw!X29</f>
+        <f>+raw!Z29</f>
         <v>0</v>
       </c>
       <c r="BR29">
-        <f>+raw!Y29</f>
+        <f>+raw!AA29</f>
         <v>0</v>
       </c>
       <c r="BT29">
-        <f>+raw!Z29</f>
+        <f>+raw!AB29</f>
         <v>0</v>
       </c>
       <c r="BV29">
-        <f>+raw!AA29</f>
+        <f>+raw!AC29</f>
         <v>0</v>
       </c>
       <c r="BX29">
-        <f>+raw!AB29</f>
+        <f>+raw!AD29</f>
         <v>0</v>
       </c>
       <c r="BZ29">
-        <f>+raw!AC29</f>
+        <f>+raw!AE29</f>
         <v>0</v>
       </c>
       <c r="CB29">
-        <f>+raw!AD29</f>
+        <f>+raw!AF29</f>
         <v>0</v>
       </c>
       <c r="CD29">
-        <f>+raw!AE29</f>
+        <f>+raw!AG29</f>
         <v>0</v>
       </c>
     </row>
@@ -15787,111 +15871,111 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <f>+raw!E30</f>
+        <f>+raw!F30</f>
         <v>0</v>
       </c>
       <c r="AG30">
-        <f>+raw!F30</f>
+        <f>+raw!H30</f>
         <v>0</v>
       </c>
       <c r="AI30">
-        <f>+raw!G30</f>
+        <f>+raw!I30</f>
         <v>0</v>
       </c>
       <c r="AK30">
-        <f>+raw!H30</f>
+        <f>+raw!J30</f>
         <v>0</v>
       </c>
       <c r="AM30">
-        <f>+raw!I30</f>
+        <f>+raw!K30</f>
         <v>0</v>
       </c>
       <c r="AO30">
-        <f>+raw!J30</f>
+        <f>+raw!L30</f>
         <v>0</v>
       </c>
       <c r="AQ30">
-        <f>+raw!K30</f>
+        <f>+raw!M30</f>
         <v>0</v>
       </c>
       <c r="AS30">
-        <f>+raw!L30</f>
+        <f>+raw!N30</f>
         <v>0</v>
       </c>
       <c r="AU30">
-        <f>+raw!M30</f>
+        <f>+raw!O30</f>
         <v>0</v>
       </c>
       <c r="AW30">
-        <f>+raw!N30</f>
+        <f>+raw!P30</f>
         <v>0</v>
       </c>
       <c r="AY30">
-        <f>+raw!O30</f>
+        <f>+raw!Q30</f>
         <v>0</v>
       </c>
       <c r="BA30">
-        <f>+raw!P30</f>
+        <f>+raw!R30</f>
         <v>0</v>
       </c>
       <c r="BC30">
-        <f>+raw!Q30</f>
+        <f>+raw!S30</f>
         <v>1</v>
       </c>
       <c r="BE30">
-        <f>+raw!R30</f>
+        <f>+raw!T30</f>
         <v>0</v>
       </c>
       <c r="BG30">
-        <f>+raw!S30</f>
+        <f>+raw!U30</f>
         <v>0</v>
       </c>
       <c r="BI30">
-        <f>+raw!T30</f>
+        <f>+raw!V30</f>
         <v>0</v>
       </c>
       <c r="BK30">
-        <f>+raw!U30</f>
+        <f>+raw!W30</f>
         <v>0</v>
       </c>
       <c r="BM30">
-        <f>+raw!V30</f>
+        <f>+raw!X30</f>
         <v>0</v>
       </c>
       <c r="BO30">
-        <f>+raw!W30</f>
+        <f>+raw!Y30</f>
         <v>0</v>
       </c>
       <c r="BQ30">
-        <f>+raw!X30</f>
+        <f>+raw!Z30</f>
         <v>0</v>
       </c>
       <c r="BS30">
-        <f>+raw!Y30</f>
+        <f>+raw!AA30</f>
         <v>0</v>
       </c>
       <c r="BU30">
-        <f>+raw!Z30</f>
+        <f>+raw!AB30</f>
         <v>0</v>
       </c>
       <c r="BW30">
-        <f>+raw!AA30</f>
+        <f>+raw!AC30</f>
         <v>0</v>
       </c>
       <c r="BY30">
-        <f>+raw!AB30</f>
+        <f>+raw!AD30</f>
         <v>0</v>
       </c>
       <c r="CA30">
-        <f>+raw!AC30</f>
+        <f>+raw!AE30</f>
         <v>0</v>
       </c>
       <c r="CC30">
-        <f>+raw!AD30</f>
+        <f>+raw!AF30</f>
         <v>0</v>
       </c>
       <c r="CE30">
-        <f>+raw!AE30</f>
+        <f>+raw!AG30</f>
         <v>0</v>
       </c>
     </row>
@@ -15901,111 +15985,111 @@
         <v>0</v>
       </c>
       <c r="AF31">
-        <f>+raw!E31</f>
+        <f>+raw!F31</f>
         <v>0</v>
       </c>
       <c r="AH31">
-        <f>+raw!F31</f>
+        <f>+raw!H31</f>
         <v>0</v>
       </c>
       <c r="AJ31">
-        <f>+raw!G31</f>
+        <f>+raw!I31</f>
         <v>0</v>
       </c>
       <c r="AL31">
-        <f>+raw!H31</f>
+        <f>+raw!J31</f>
         <v>0</v>
       </c>
       <c r="AN31">
-        <f>+raw!I31</f>
+        <f>+raw!K31</f>
         <v>0</v>
       </c>
       <c r="AP31">
-        <f>+raw!J31</f>
+        <f>+raw!L31</f>
         <v>0</v>
       </c>
       <c r="AR31">
-        <f>+raw!K31</f>
+        <f>+raw!M31</f>
         <v>0</v>
       </c>
       <c r="AT31">
-        <f>+raw!L31</f>
+        <f>+raw!N31</f>
         <v>0</v>
       </c>
       <c r="AV31">
-        <f>+raw!M31</f>
+        <f>+raw!O31</f>
         <v>0</v>
       </c>
       <c r="AX31">
-        <f>+raw!N31</f>
+        <f>+raw!P31</f>
         <v>0</v>
       </c>
       <c r="AZ31">
-        <f>+raw!O31</f>
+        <f>+raw!Q31</f>
         <v>0</v>
       </c>
       <c r="BB31">
-        <f>+raw!P31</f>
+        <f>+raw!R31</f>
         <v>1</v>
       </c>
       <c r="BD31">
-        <f>+raw!Q31</f>
+        <f>+raw!S31</f>
         <v>1</v>
       </c>
       <c r="BF31">
-        <f>+raw!R31</f>
+        <f>+raw!T31</f>
         <v>0</v>
       </c>
       <c r="BH31">
-        <f>+raw!S31</f>
+        <f>+raw!U31</f>
         <v>0</v>
       </c>
       <c r="BJ31">
-        <f>+raw!T31</f>
+        <f>+raw!V31</f>
         <v>0</v>
       </c>
       <c r="BL31">
-        <f>+raw!U31</f>
+        <f>+raw!W31</f>
         <v>0</v>
       </c>
       <c r="BN31">
-        <f>+raw!V31</f>
+        <f>+raw!X31</f>
         <v>0</v>
       </c>
       <c r="BP31">
-        <f>+raw!W31</f>
+        <f>+raw!Y31</f>
         <v>0</v>
       </c>
       <c r="BR31">
-        <f>+raw!X31</f>
+        <f>+raw!Z31</f>
         <v>0</v>
       </c>
       <c r="BT31">
-        <f>+raw!Y31</f>
+        <f>+raw!AA31</f>
         <v>0</v>
       </c>
       <c r="BV31">
-        <f>+raw!Z31</f>
+        <f>+raw!AB31</f>
         <v>0</v>
       </c>
       <c r="BX31">
-        <f>+raw!AA31</f>
+        <f>+raw!AC31</f>
         <v>0</v>
       </c>
       <c r="BZ31">
-        <f>+raw!AB31</f>
+        <f>+raw!AD31</f>
         <v>0</v>
       </c>
       <c r="CB31">
-        <f>+raw!AC31</f>
+        <f>+raw!AE31</f>
         <v>0</v>
       </c>
       <c r="CD31">
-        <f>+raw!AD31</f>
+        <f>+raw!AF31</f>
         <v>0</v>
       </c>
       <c r="CF31">
-        <f>+raw!AE31</f>
+        <f>+raw!AG31</f>
         <v>0</v>
       </c>
     </row>
@@ -16015,111 +16099,111 @@
         <v>0</v>
       </c>
       <c r="AG32">
-        <f>+raw!E32</f>
+        <f>+raw!F32</f>
         <v>0</v>
       </c>
       <c r="AI32">
-        <f>+raw!F32</f>
+        <f>+raw!H32</f>
         <v>0</v>
       </c>
       <c r="AK32">
-        <f>+raw!G32</f>
+        <f>+raw!I32</f>
         <v>0</v>
       </c>
       <c r="AM32">
-        <f>+raw!H32</f>
+        <f>+raw!J32</f>
         <v>0</v>
       </c>
       <c r="AO32">
-        <f>+raw!I32</f>
+        <f>+raw!K32</f>
         <v>0</v>
       </c>
       <c r="AQ32">
-        <f>+raw!J32</f>
+        <f>+raw!L32</f>
         <v>0</v>
       </c>
       <c r="AS32">
-        <f>+raw!K32</f>
+        <f>+raw!M32</f>
         <v>0</v>
       </c>
       <c r="AU32">
-        <f>+raw!L32</f>
+        <f>+raw!N32</f>
         <v>0</v>
       </c>
       <c r="AW32">
-        <f>+raw!M32</f>
+        <f>+raw!O32</f>
         <v>0</v>
       </c>
       <c r="AY32">
-        <f>+raw!N32</f>
+        <f>+raw!P32</f>
         <v>0</v>
       </c>
       <c r="BA32">
-        <f>+raw!O32</f>
+        <f>+raw!Q32</f>
         <v>0</v>
       </c>
       <c r="BC32">
-        <f>+raw!P32</f>
+        <f>+raw!R32</f>
         <v>1</v>
       </c>
       <c r="BE32">
-        <f>+raw!Q32</f>
+        <f>+raw!S32</f>
         <v>0</v>
       </c>
       <c r="BG32">
-        <f>+raw!R32</f>
+        <f>+raw!T32</f>
         <v>0</v>
       </c>
       <c r="BI32">
-        <f>+raw!S32</f>
+        <f>+raw!U32</f>
         <v>0</v>
       </c>
       <c r="BK32">
-        <f>+raw!T32</f>
+        <f>+raw!V32</f>
         <v>0</v>
       </c>
       <c r="BM32">
-        <f>+raw!U32</f>
+        <f>+raw!W32</f>
         <v>0</v>
       </c>
       <c r="BO32">
-        <f>+raw!V32</f>
+        <f>+raw!X32</f>
         <v>0</v>
       </c>
       <c r="BQ32">
-        <f>+raw!W32</f>
+        <f>+raw!Y32</f>
         <v>0</v>
       </c>
       <c r="BS32">
-        <f>+raw!X32</f>
+        <f>+raw!Z32</f>
         <v>0</v>
       </c>
       <c r="BU32">
-        <f>+raw!Y32</f>
+        <f>+raw!AA32</f>
         <v>0</v>
       </c>
       <c r="BW32">
-        <f>+raw!Z32</f>
+        <f>+raw!AB32</f>
         <v>0</v>
       </c>
       <c r="BY32">
-        <f>+raw!AA32</f>
+        <f>+raw!AC32</f>
         <v>0</v>
       </c>
       <c r="CA32">
-        <f>+raw!AB32</f>
+        <f>+raw!AD32</f>
         <v>0</v>
       </c>
       <c r="CC32">
-        <f>+raw!AC32</f>
+        <f>+raw!AE32</f>
         <v>0</v>
       </c>
       <c r="CE32">
-        <f>+raw!AD32</f>
+        <f>+raw!AF32</f>
         <v>0</v>
       </c>
       <c r="CG32">
-        <f>+raw!AE32</f>
+        <f>+raw!AG32</f>
         <v>0</v>
       </c>
     </row>
@@ -16129,111 +16213,111 @@
         <v>0</v>
       </c>
       <c r="AH33">
-        <f>+raw!E33</f>
+        <f>+raw!F33</f>
         <v>0</v>
       </c>
       <c r="AJ33">
-        <f>+raw!F33</f>
+        <f>+raw!H33</f>
         <v>0</v>
       </c>
       <c r="AL33">
-        <f>+raw!G33</f>
+        <f>+raw!I33</f>
         <v>0</v>
       </c>
       <c r="AN33">
-        <f>+raw!H33</f>
+        <f>+raw!J33</f>
         <v>0</v>
       </c>
       <c r="AP33">
-        <f>+raw!I33</f>
+        <f>+raw!K33</f>
         <v>0</v>
       </c>
       <c r="AR33">
-        <f>+raw!J33</f>
+        <f>+raw!L33</f>
         <v>0</v>
       </c>
       <c r="AT33">
-        <f>+raw!K33</f>
+        <f>+raw!M33</f>
         <v>0</v>
       </c>
       <c r="AV33">
-        <f>+raw!L33</f>
+        <f>+raw!N33</f>
         <v>0</v>
       </c>
       <c r="AX33">
-        <f>+raw!M33</f>
+        <f>+raw!O33</f>
         <v>0</v>
       </c>
       <c r="AZ33">
-        <f>+raw!N33</f>
+        <f>+raw!P33</f>
         <v>0</v>
       </c>
       <c r="BB33">
-        <f>+raw!O33</f>
+        <f>+raw!Q33</f>
         <v>0</v>
       </c>
       <c r="BD33">
-        <f>+raw!P33</f>
+        <f>+raw!R33</f>
         <v>1</v>
       </c>
       <c r="BF33">
-        <f>+raw!Q33</f>
+        <f>+raw!S33</f>
         <v>0</v>
       </c>
       <c r="BH33">
-        <f>+raw!R33</f>
+        <f>+raw!T33</f>
         <v>0</v>
       </c>
       <c r="BJ33">
-        <f>+raw!S33</f>
+        <f>+raw!U33</f>
         <v>0</v>
       </c>
       <c r="BL33">
-        <f>+raw!T33</f>
+        <f>+raw!V33</f>
         <v>0</v>
       </c>
       <c r="BN33">
-        <f>+raw!U33</f>
+        <f>+raw!W33</f>
         <v>0</v>
       </c>
       <c r="BP33">
-        <f>+raw!V33</f>
+        <f>+raw!X33</f>
         <v>0</v>
       </c>
       <c r="BR33">
-        <f>+raw!W33</f>
+        <f>+raw!Y33</f>
         <v>0</v>
       </c>
       <c r="BT33">
-        <f>+raw!X33</f>
+        <f>+raw!Z33</f>
         <v>0</v>
       </c>
       <c r="BV33">
-        <f>+raw!Y33</f>
+        <f>+raw!AA33</f>
         <v>0</v>
       </c>
       <c r="BX33">
-        <f>+raw!Z33</f>
+        <f>+raw!AB33</f>
         <v>0</v>
       </c>
       <c r="BZ33">
-        <f>+raw!AA33</f>
+        <f>+raw!AC33</f>
         <v>0</v>
       </c>
       <c r="CB33">
-        <f>+raw!AB33</f>
+        <f>+raw!AD33</f>
         <v>0</v>
       </c>
       <c r="CD33">
-        <f>+raw!AC33</f>
+        <f>+raw!AE33</f>
         <v>0</v>
       </c>
       <c r="CF33">
-        <f>+raw!AD33</f>
+        <f>+raw!AF33</f>
         <v>0</v>
       </c>
       <c r="CH33">
-        <f>+raw!AE33</f>
+        <f>+raw!AG33</f>
         <v>0</v>
       </c>
     </row>
@@ -16243,111 +16327,111 @@
         <v>0</v>
       </c>
       <c r="AI34">
-        <f>+raw!E34</f>
+        <f>+raw!F34</f>
         <v>0</v>
       </c>
       <c r="AK34">
-        <f>+raw!F34</f>
+        <f>+raw!H34</f>
         <v>0</v>
       </c>
       <c r="AM34">
-        <f>+raw!G34</f>
+        <f>+raw!I34</f>
         <v>0</v>
       </c>
       <c r="AO34">
-        <f>+raw!H34</f>
+        <f>+raw!J34</f>
         <v>0</v>
       </c>
       <c r="AQ34">
-        <f>+raw!I34</f>
+        <f>+raw!K34</f>
         <v>0</v>
       </c>
       <c r="AS34">
-        <f>+raw!J34</f>
+        <f>+raw!L34</f>
         <v>0</v>
       </c>
       <c r="AU34">
-        <f>+raw!K34</f>
+        <f>+raw!M34</f>
         <v>0</v>
       </c>
       <c r="AW34">
-        <f>+raw!L34</f>
+        <f>+raw!N34</f>
         <v>0</v>
       </c>
       <c r="AY34">
-        <f>+raw!M34</f>
+        <f>+raw!O34</f>
         <v>0</v>
       </c>
       <c r="BA34">
-        <f>+raw!N34</f>
+        <f>+raw!P34</f>
         <v>0</v>
       </c>
       <c r="BC34">
-        <f>+raw!O34</f>
+        <f>+raw!Q34</f>
         <v>0</v>
       </c>
       <c r="BE34">
-        <f>+raw!P34</f>
+        <f>+raw!R34</f>
         <v>0</v>
       </c>
       <c r="BG34">
-        <f>+raw!Q34</f>
+        <f>+raw!S34</f>
         <v>0</v>
       </c>
       <c r="BI34">
-        <f>+raw!R34</f>
+        <f>+raw!T34</f>
         <v>0</v>
       </c>
       <c r="BK34">
-        <f>+raw!S34</f>
+        <f>+raw!U34</f>
         <v>0</v>
       </c>
       <c r="BM34">
-        <f>+raw!T34</f>
+        <f>+raw!V34</f>
         <v>0</v>
       </c>
       <c r="BO34">
-        <f>+raw!U34</f>
+        <f>+raw!W34</f>
         <v>0</v>
       </c>
       <c r="BQ34">
-        <f>+raw!V34</f>
+        <f>+raw!X34</f>
         <v>0</v>
       </c>
       <c r="BS34">
-        <f>+raw!W34</f>
+        <f>+raw!Y34</f>
         <v>0</v>
       </c>
       <c r="BU34">
-        <f>+raw!X34</f>
+        <f>+raw!Z34</f>
         <v>0</v>
       </c>
       <c r="BW34">
-        <f>+raw!Y34</f>
+        <f>+raw!AA34</f>
         <v>0</v>
       </c>
       <c r="BY34">
-        <f>+raw!Z34</f>
+        <f>+raw!AB34</f>
         <v>0</v>
       </c>
       <c r="CA34">
-        <f>+raw!AA34</f>
+        <f>+raw!AC34</f>
         <v>0</v>
       </c>
       <c r="CC34">
-        <f>+raw!AB34</f>
+        <f>+raw!AD34</f>
         <v>0</v>
       </c>
       <c r="CE34">
-        <f>+raw!AC34</f>
+        <f>+raw!AE34</f>
         <v>0</v>
       </c>
       <c r="CG34">
-        <f>+raw!AD34</f>
+        <f>+raw!AF34</f>
         <v>0</v>
       </c>
       <c r="CI34">
-        <f>+raw!AE34</f>
+        <f>+raw!AG34</f>
         <v>0</v>
       </c>
     </row>
@@ -16357,111 +16441,111 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <f>+raw!E35</f>
+        <f>+raw!F35</f>
         <v>0</v>
       </c>
       <c r="AL35">
-        <f>+raw!F35</f>
+        <f>+raw!H35</f>
         <v>0</v>
       </c>
       <c r="AN35">
-        <f>+raw!G35</f>
+        <f>+raw!I35</f>
         <v>0</v>
       </c>
       <c r="AP35">
-        <f>+raw!H35</f>
+        <f>+raw!J35</f>
         <v>0</v>
       </c>
       <c r="AR35">
-        <f>+raw!I35</f>
+        <f>+raw!K35</f>
         <v>0</v>
       </c>
       <c r="AT35">
-        <f>+raw!J35</f>
+        <f>+raw!L35</f>
         <v>0</v>
       </c>
       <c r="AV35">
-        <f>+raw!K35</f>
+        <f>+raw!M35</f>
         <v>0</v>
       </c>
       <c r="AX35">
-        <f>+raw!L35</f>
+        <f>+raw!N35</f>
         <v>0</v>
       </c>
       <c r="AZ35">
-        <f>+raw!M35</f>
+        <f>+raw!O35</f>
         <v>0</v>
       </c>
       <c r="BB35">
-        <f>+raw!N35</f>
+        <f>+raw!P35</f>
         <v>0</v>
       </c>
       <c r="BD35">
-        <f>+raw!O35</f>
+        <f>+raw!Q35</f>
         <v>0</v>
       </c>
       <c r="BF35">
-        <f>+raw!P35</f>
+        <f>+raw!R35</f>
         <v>0</v>
       </c>
       <c r="BH35">
-        <f>+raw!Q35</f>
+        <f>+raw!S35</f>
         <v>0</v>
       </c>
       <c r="BJ35">
-        <f>+raw!R35</f>
+        <f>+raw!T35</f>
         <v>0</v>
       </c>
       <c r="BL35">
-        <f>+raw!S35</f>
+        <f>+raw!U35</f>
         <v>0</v>
       </c>
       <c r="BN35">
-        <f>+raw!T35</f>
+        <f>+raw!V35</f>
         <v>0</v>
       </c>
       <c r="BP35">
-        <f>+raw!U35</f>
+        <f>+raw!W35</f>
         <v>0</v>
       </c>
       <c r="BR35">
-        <f>+raw!V35</f>
+        <f>+raw!X35</f>
         <v>0</v>
       </c>
       <c r="BT35">
-        <f>+raw!W35</f>
+        <f>+raw!Y35</f>
         <v>0</v>
       </c>
       <c r="BV35">
-        <f>+raw!X35</f>
+        <f>+raw!Z35</f>
         <v>0</v>
       </c>
       <c r="BX35">
-        <f>+raw!Y35</f>
+        <f>+raw!AA35</f>
         <v>0</v>
       </c>
       <c r="BZ35">
-        <f>+raw!Z35</f>
+        <f>+raw!AB35</f>
         <v>0</v>
       </c>
       <c r="CB35">
-        <f>+raw!AA35</f>
+        <f>+raw!AC35</f>
         <v>0</v>
       </c>
       <c r="CD35">
-        <f>+raw!AB35</f>
+        <f>+raw!AD35</f>
         <v>0</v>
       </c>
       <c r="CF35">
-        <f>+raw!AC35</f>
+        <f>+raw!AE35</f>
         <v>0</v>
       </c>
       <c r="CH35">
-        <f>+raw!AD35</f>
+        <f>+raw!AF35</f>
         <v>0</v>
       </c>
       <c r="CJ35">
-        <f>+raw!AE35</f>
+        <f>+raw!AG35</f>
         <v>0</v>
       </c>
     </row>
@@ -16471,111 +16555,111 @@
         <v>0</v>
       </c>
       <c r="AK36">
-        <f>+raw!E36</f>
+        <f>+raw!F36</f>
         <v>0</v>
       </c>
       <c r="AM36">
-        <f>+raw!F36</f>
+        <f>+raw!H36</f>
         <v>0</v>
       </c>
       <c r="AO36">
-        <f>+raw!G36</f>
+        <f>+raw!I36</f>
         <v>0</v>
       </c>
       <c r="AQ36">
-        <f>+raw!H36</f>
+        <f>+raw!J36</f>
         <v>0</v>
       </c>
       <c r="AS36">
-        <f>+raw!I36</f>
+        <f>+raw!K36</f>
         <v>0</v>
       </c>
       <c r="AU36">
-        <f>+raw!J36</f>
+        <f>+raw!L36</f>
         <v>0</v>
       </c>
       <c r="AW36">
-        <f>+raw!K36</f>
+        <f>+raw!M36</f>
         <v>0</v>
       </c>
       <c r="AY36">
-        <f>+raw!L36</f>
+        <f>+raw!N36</f>
         <v>0</v>
       </c>
       <c r="BA36">
-        <f>+raw!M36</f>
+        <f>+raw!O36</f>
         <v>0</v>
       </c>
       <c r="BC36">
-        <f>+raw!N36</f>
+        <f>+raw!P36</f>
         <v>0</v>
       </c>
       <c r="BE36">
-        <f>+raw!O36</f>
+        <f>+raw!Q36</f>
         <v>0</v>
       </c>
       <c r="BG36">
-        <f>+raw!P36</f>
+        <f>+raw!R36</f>
         <v>0</v>
       </c>
       <c r="BI36">
-        <f>+raw!Q36</f>
+        <f>+raw!S36</f>
         <v>0</v>
       </c>
       <c r="BK36">
-        <f>+raw!R36</f>
+        <f>+raw!T36</f>
         <v>0</v>
       </c>
       <c r="BM36">
-        <f>+raw!S36</f>
+        <f>+raw!U36</f>
         <v>0</v>
       </c>
       <c r="BO36">
-        <f>+raw!T36</f>
+        <f>+raw!V36</f>
         <v>0</v>
       </c>
       <c r="BQ36">
-        <f>+raw!U36</f>
+        <f>+raw!W36</f>
         <v>0</v>
       </c>
       <c r="BS36">
-        <f>+raw!V36</f>
+        <f>+raw!X36</f>
         <v>0</v>
       </c>
       <c r="BU36">
-        <f>+raw!W36</f>
+        <f>+raw!Y36</f>
         <v>0</v>
       </c>
       <c r="BW36">
-        <f>+raw!X36</f>
+        <f>+raw!Z36</f>
         <v>0</v>
       </c>
       <c r="BY36">
-        <f>+raw!Y36</f>
+        <f>+raw!AA36</f>
         <v>0</v>
       </c>
       <c r="CA36">
-        <f>+raw!Z36</f>
+        <f>+raw!AB36</f>
         <v>0</v>
       </c>
       <c r="CC36">
-        <f>+raw!AA36</f>
+        <f>+raw!AC36</f>
         <v>0</v>
       </c>
       <c r="CE36">
-        <f>+raw!AB36</f>
+        <f>+raw!AD36</f>
         <v>0</v>
       </c>
       <c r="CG36">
-        <f>+raw!AC36</f>
+        <f>+raw!AE36</f>
         <v>0</v>
       </c>
       <c r="CI36">
-        <f>+raw!AD36</f>
+        <f>+raw!AF36</f>
         <v>0</v>
       </c>
       <c r="CK36">
-        <f>+raw!AE36</f>
+        <f>+raw!AG36</f>
         <v>0</v>
       </c>
     </row>
@@ -16585,111 +16669,111 @@
         <v>0</v>
       </c>
       <c r="AL37">
-        <f>+raw!E37</f>
+        <f>+raw!F37</f>
         <v>0</v>
       </c>
       <c r="AN37">
-        <f>+raw!F37</f>
+        <f>+raw!H37</f>
         <v>0</v>
       </c>
       <c r="AP37">
-        <f>+raw!G37</f>
+        <f>+raw!I37</f>
         <v>0</v>
       </c>
       <c r="AR37">
-        <f>+raw!H37</f>
+        <f>+raw!J37</f>
         <v>0</v>
       </c>
       <c r="AT37">
-        <f>+raw!I37</f>
+        <f>+raw!K37</f>
         <v>0</v>
       </c>
       <c r="AV37">
-        <f>+raw!J37</f>
+        <f>+raw!L37</f>
         <v>0</v>
       </c>
       <c r="AX37">
-        <f>+raw!K37</f>
+        <f>+raw!M37</f>
         <v>0</v>
       </c>
       <c r="AZ37">
-        <f>+raw!L37</f>
+        <f>+raw!N37</f>
         <v>0</v>
       </c>
       <c r="BB37">
-        <f>+raw!M37</f>
+        <f>+raw!O37</f>
         <v>0</v>
       </c>
       <c r="BD37">
-        <f>+raw!N37</f>
+        <f>+raw!P37</f>
         <v>0</v>
       </c>
       <c r="BF37">
-        <f>+raw!O37</f>
+        <f>+raw!Q37</f>
         <v>0</v>
       </c>
       <c r="BH37">
-        <f>+raw!P37</f>
+        <f>+raw!R37</f>
         <v>0</v>
       </c>
       <c r="BJ37">
-        <f>+raw!Q37</f>
+        <f>+raw!S37</f>
         <v>0</v>
       </c>
       <c r="BL37">
-        <f>+raw!R37</f>
+        <f>+raw!T37</f>
         <v>0</v>
       </c>
       <c r="BN37">
-        <f>+raw!S37</f>
+        <f>+raw!U37</f>
         <v>0</v>
       </c>
       <c r="BP37">
-        <f>+raw!T37</f>
+        <f>+raw!V37</f>
         <v>0</v>
       </c>
       <c r="BR37">
-        <f>+raw!U37</f>
+        <f>+raw!W37</f>
         <v>0</v>
       </c>
       <c r="BT37">
-        <f>+raw!V37</f>
+        <f>+raw!X37</f>
         <v>0</v>
       </c>
       <c r="BV37">
-        <f>+raw!W37</f>
+        <f>+raw!Y37</f>
         <v>0</v>
       </c>
       <c r="BX37">
-        <f>+raw!X37</f>
+        <f>+raw!Z37</f>
         <v>0</v>
       </c>
       <c r="BZ37">
-        <f>+raw!Y37</f>
+        <f>+raw!AA37</f>
         <v>0</v>
       </c>
       <c r="CB37">
-        <f>+raw!Z37</f>
+        <f>+raw!AB37</f>
         <v>0</v>
       </c>
       <c r="CD37">
-        <f>+raw!AA37</f>
+        <f>+raw!AC37</f>
         <v>0</v>
       </c>
       <c r="CF37">
-        <f>+raw!AB37</f>
+        <f>+raw!AD37</f>
         <v>0</v>
       </c>
       <c r="CH37">
-        <f>+raw!AC37</f>
+        <f>+raw!AE37</f>
         <v>0</v>
       </c>
       <c r="CJ37">
-        <f>+raw!AD37</f>
+        <f>+raw!AF37</f>
         <v>0</v>
       </c>
       <c r="CL37">
-        <f>+raw!AE37</f>
+        <f>+raw!AG37</f>
         <v>0</v>
       </c>
     </row>
@@ -16699,111 +16783,111 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <f>+raw!E38</f>
+        <f>+raw!F38</f>
         <v>0</v>
       </c>
       <c r="AO38">
-        <f>+raw!F38</f>
+        <f>+raw!H38</f>
         <v>0</v>
       </c>
       <c r="AQ38">
-        <f>+raw!G38</f>
+        <f>+raw!I38</f>
         <v>0</v>
       </c>
       <c r="AS38">
-        <f>+raw!H38</f>
+        <f>+raw!J38</f>
         <v>0</v>
       </c>
       <c r="AU38">
-        <f>+raw!I38</f>
+        <f>+raw!K38</f>
         <v>0</v>
       </c>
       <c r="AW38">
-        <f>+raw!J38</f>
+        <f>+raw!L38</f>
         <v>0</v>
       </c>
       <c r="AY38">
-        <f>+raw!K38</f>
+        <f>+raw!M38</f>
         <v>0</v>
       </c>
       <c r="BA38">
-        <f>+raw!L38</f>
+        <f>+raw!N38</f>
         <v>0</v>
       </c>
       <c r="BC38">
-        <f>+raw!M38</f>
+        <f>+raw!O38</f>
         <v>0</v>
       </c>
       <c r="BE38">
-        <f>+raw!N38</f>
+        <f>+raw!P38</f>
         <v>0</v>
       </c>
       <c r="BG38">
-        <f>+raw!O38</f>
+        <f>+raw!Q38</f>
         <v>0</v>
       </c>
       <c r="BI38">
-        <f>+raw!P38</f>
+        <f>+raw!R38</f>
         <v>0</v>
       </c>
       <c r="BK38">
-        <f>+raw!Q38</f>
+        <f>+raw!S38</f>
         <v>0</v>
       </c>
       <c r="BM38">
-        <f>+raw!R38</f>
+        <f>+raw!T38</f>
         <v>0</v>
       </c>
       <c r="BO38">
-        <f>+raw!S38</f>
+        <f>+raw!U38</f>
         <v>0</v>
       </c>
       <c r="BQ38">
-        <f>+raw!T38</f>
+        <f>+raw!V38</f>
         <v>0</v>
       </c>
       <c r="BS38">
-        <f>+raw!U38</f>
+        <f>+raw!W38</f>
         <v>0</v>
       </c>
       <c r="BU38">
-        <f>+raw!V38</f>
+        <f>+raw!X38</f>
         <v>0</v>
       </c>
       <c r="BW38">
-        <f>+raw!W38</f>
+        <f>+raw!Y38</f>
         <v>0</v>
       </c>
       <c r="BY38">
-        <f>+raw!X38</f>
+        <f>+raw!Z38</f>
         <v>0</v>
       </c>
       <c r="CA38">
-        <f>+raw!Y38</f>
+        <f>+raw!AA38</f>
         <v>0</v>
       </c>
       <c r="CC38">
-        <f>+raw!Z38</f>
+        <f>+raw!AB38</f>
         <v>0</v>
       </c>
       <c r="CE38">
-        <f>+raw!AA38</f>
+        <f>+raw!AC38</f>
         <v>0</v>
       </c>
       <c r="CG38">
-        <f>+raw!AB38</f>
+        <f>+raw!AD38</f>
         <v>0</v>
       </c>
       <c r="CI38">
-        <f>+raw!AC38</f>
+        <f>+raw!AE38</f>
         <v>0</v>
       </c>
       <c r="CK38">
-        <f>+raw!AD38</f>
+        <f>+raw!AF38</f>
         <v>0</v>
       </c>
       <c r="CM38">
-        <f>+raw!AE38</f>
+        <f>+raw!AG38</f>
         <v>0</v>
       </c>
     </row>
@@ -16813,111 +16897,111 @@
         <v>0</v>
       </c>
       <c r="AN39">
-        <f>+raw!E39</f>
+        <f>+raw!F39</f>
         <v>0</v>
       </c>
       <c r="AP39">
-        <f>+raw!F39</f>
+        <f>+raw!H39</f>
         <v>0</v>
       </c>
       <c r="AR39">
-        <f>+raw!G39</f>
+        <f>+raw!I39</f>
         <v>0</v>
       </c>
       <c r="AT39">
-        <f>+raw!H39</f>
+        <f>+raw!J39</f>
         <v>0</v>
       </c>
       <c r="AV39">
-        <f>+raw!I39</f>
+        <f>+raw!K39</f>
         <v>0</v>
       </c>
       <c r="AX39">
-        <f>+raw!J39</f>
+        <f>+raw!L39</f>
         <v>0</v>
       </c>
       <c r="AZ39">
-        <f>+raw!K39</f>
+        <f>+raw!M39</f>
         <v>0</v>
       </c>
       <c r="BB39">
-        <f>+raw!L39</f>
+        <f>+raw!N39</f>
         <v>0</v>
       </c>
       <c r="BD39">
-        <f>+raw!M39</f>
+        <f>+raw!O39</f>
         <v>0</v>
       </c>
       <c r="BF39">
-        <f>+raw!N39</f>
+        <f>+raw!P39</f>
         <v>0</v>
       </c>
       <c r="BH39">
-        <f>+raw!O39</f>
+        <f>+raw!Q39</f>
         <v>0</v>
       </c>
       <c r="BJ39">
-        <f>+raw!P39</f>
+        <f>+raw!R39</f>
         <v>0</v>
       </c>
       <c r="BL39">
-        <f>+raw!Q39</f>
+        <f>+raw!S39</f>
         <v>0</v>
       </c>
       <c r="BN39">
-        <f>+raw!R39</f>
+        <f>+raw!T39</f>
         <v>0</v>
       </c>
       <c r="BP39">
-        <f>+raw!S39</f>
+        <f>+raw!U39</f>
         <v>0</v>
       </c>
       <c r="BR39">
-        <f>+raw!T39</f>
+        <f>+raw!V39</f>
         <v>0</v>
       </c>
       <c r="BT39">
-        <f>+raw!U39</f>
+        <f>+raw!W39</f>
         <v>0</v>
       </c>
       <c r="BV39">
-        <f>+raw!V39</f>
+        <f>+raw!X39</f>
         <v>0</v>
       </c>
       <c r="BX39">
-        <f>+raw!W39</f>
+        <f>+raw!Y39</f>
         <v>0</v>
       </c>
       <c r="BZ39">
-        <f>+raw!X39</f>
+        <f>+raw!Z39</f>
         <v>0</v>
       </c>
       <c r="CB39">
-        <f>+raw!Y39</f>
+        <f>+raw!AA39</f>
         <v>0</v>
       </c>
       <c r="CD39">
-        <f>+raw!Z39</f>
+        <f>+raw!AB39</f>
         <v>0</v>
       </c>
       <c r="CF39">
-        <f>+raw!AA39</f>
+        <f>+raw!AC39</f>
         <v>0</v>
       </c>
       <c r="CH39">
-        <f>+raw!AB39</f>
+        <f>+raw!AD39</f>
         <v>0</v>
       </c>
       <c r="CJ39">
-        <f>+raw!AC39</f>
+        <f>+raw!AE39</f>
         <v>0</v>
       </c>
       <c r="CL39">
-        <f>+raw!AD39</f>
+        <f>+raw!AF39</f>
         <v>0</v>
       </c>
       <c r="CN39">
-        <f>+raw!AE39</f>
+        <f>+raw!AG39</f>
         <v>0</v>
       </c>
     </row>
@@ -16927,111 +17011,111 @@
         <v>0</v>
       </c>
       <c r="AO40">
-        <f>+raw!E40</f>
+        <f>+raw!F40</f>
         <v>0</v>
       </c>
       <c r="AQ40">
-        <f>+raw!F40</f>
+        <f>+raw!H40</f>
         <v>0</v>
       </c>
       <c r="AS40">
-        <f>+raw!G40</f>
+        <f>+raw!I40</f>
         <v>0</v>
       </c>
       <c r="AU40">
-        <f>+raw!H40</f>
+        <f>+raw!J40</f>
         <v>0</v>
       </c>
       <c r="AW40">
-        <f>+raw!I40</f>
+        <f>+raw!K40</f>
         <v>0</v>
       </c>
       <c r="AY40">
-        <f>+raw!J40</f>
+        <f>+raw!L40</f>
         <v>0</v>
       </c>
       <c r="BA40">
-        <f>+raw!K40</f>
+        <f>+raw!M40</f>
         <v>0</v>
       </c>
       <c r="BC40">
-        <f>+raw!L40</f>
+        <f>+raw!N40</f>
         <v>0</v>
       </c>
       <c r="BE40">
-        <f>+raw!M40</f>
+        <f>+raw!O40</f>
         <v>0</v>
       </c>
       <c r="BG40">
-        <f>+raw!N40</f>
+        <f>+raw!P40</f>
         <v>0</v>
       </c>
       <c r="BI40">
-        <f>+raw!O40</f>
+        <f>+raw!Q40</f>
         <v>0</v>
       </c>
       <c r="BK40">
-        <f>+raw!P40</f>
+        <f>+raw!R40</f>
         <v>0</v>
       </c>
       <c r="BM40">
-        <f>+raw!Q40</f>
+        <f>+raw!S40</f>
         <v>0</v>
       </c>
       <c r="BO40">
-        <f>+raw!R40</f>
+        <f>+raw!T40</f>
         <v>0</v>
       </c>
       <c r="BQ40">
-        <f>+raw!S40</f>
+        <f>+raw!U40</f>
         <v>0</v>
       </c>
       <c r="BS40">
-        <f>+raw!T40</f>
+        <f>+raw!V40</f>
         <v>0</v>
       </c>
       <c r="BU40">
-        <f>+raw!U40</f>
+        <f>+raw!W40</f>
         <v>0</v>
       </c>
       <c r="BW40">
-        <f>+raw!V40</f>
+        <f>+raw!X40</f>
         <v>0</v>
       </c>
       <c r="BY40">
-        <f>+raw!W40</f>
+        <f>+raw!Y40</f>
         <v>0</v>
       </c>
       <c r="CA40">
-        <f>+raw!X40</f>
+        <f>+raw!Z40</f>
         <v>0</v>
       </c>
       <c r="CC40">
-        <f>+raw!Y40</f>
+        <f>+raw!AA40</f>
         <v>0</v>
       </c>
       <c r="CE40">
-        <f>+raw!Z40</f>
+        <f>+raw!AB40</f>
         <v>0</v>
       </c>
       <c r="CG40">
-        <f>+raw!AA40</f>
+        <f>+raw!AC40</f>
         <v>0</v>
       </c>
       <c r="CI40">
-        <f>+raw!AB40</f>
+        <f>+raw!AD40</f>
         <v>0</v>
       </c>
       <c r="CK40">
-        <f>+raw!AC40</f>
+        <f>+raw!AE40</f>
         <v>0</v>
       </c>
       <c r="CM40">
-        <f>+raw!AD40</f>
+        <f>+raw!AF40</f>
         <v>0</v>
       </c>
       <c r="CO40">
-        <f>+raw!AE40</f>
+        <f>+raw!AG40</f>
         <v>0</v>
       </c>
     </row>
@@ -17041,111 +17125,111 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <f>+raw!E41</f>
+        <f>+raw!F41</f>
         <v>0</v>
       </c>
       <c r="AR41">
-        <f>+raw!F41</f>
+        <f>+raw!H41</f>
         <v>0</v>
       </c>
       <c r="AT41">
-        <f>+raw!G41</f>
+        <f>+raw!I41</f>
         <v>0</v>
       </c>
       <c r="AV41">
-        <f>+raw!H41</f>
+        <f>+raw!J41</f>
         <v>0</v>
       </c>
       <c r="AX41">
-        <f>+raw!I41</f>
+        <f>+raw!K41</f>
         <v>0</v>
       </c>
       <c r="AZ41">
-        <f>+raw!J41</f>
+        <f>+raw!L41</f>
         <v>0</v>
       </c>
       <c r="BB41">
-        <f>+raw!K41</f>
+        <f>+raw!M41</f>
         <v>0</v>
       </c>
       <c r="BD41">
-        <f>+raw!L41</f>
+        <f>+raw!N41</f>
         <v>0</v>
       </c>
       <c r="BF41">
-        <f>+raw!M41</f>
+        <f>+raw!O41</f>
         <v>0</v>
       </c>
       <c r="BH41">
-        <f>+raw!N41</f>
+        <f>+raw!P41</f>
         <v>0</v>
       </c>
       <c r="BJ41">
-        <f>+raw!O41</f>
+        <f>+raw!Q41</f>
         <v>0</v>
       </c>
       <c r="BL41">
-        <f>+raw!P41</f>
+        <f>+raw!R41</f>
         <v>0</v>
       </c>
       <c r="BN41">
-        <f>+raw!Q41</f>
+        <f>+raw!S41</f>
         <v>0</v>
       </c>
       <c r="BP41">
-        <f>+raw!R41</f>
+        <f>+raw!T41</f>
         <v>0</v>
       </c>
       <c r="BR41">
-        <f>+raw!S41</f>
+        <f>+raw!U41</f>
         <v>0</v>
       </c>
       <c r="BT41">
-        <f>+raw!T41</f>
+        <f>+raw!V41</f>
         <v>0</v>
       </c>
       <c r="BV41">
-        <f>+raw!U41</f>
+        <f>+raw!W41</f>
         <v>0</v>
       </c>
       <c r="BX41">
-        <f>+raw!V41</f>
+        <f>+raw!X41</f>
         <v>0</v>
       </c>
       <c r="BZ41">
-        <f>+raw!W41</f>
+        <f>+raw!Y41</f>
         <v>0</v>
       </c>
       <c r="CB41">
-        <f>+raw!X41</f>
+        <f>+raw!Z41</f>
         <v>0</v>
       </c>
       <c r="CD41">
-        <f>+raw!Y41</f>
+        <f>+raw!AA41</f>
         <v>0</v>
       </c>
       <c r="CF41">
-        <f>+raw!Z41</f>
+        <f>+raw!AB41</f>
         <v>0</v>
       </c>
       <c r="CH41">
-        <f>+raw!AA41</f>
+        <f>+raw!AC41</f>
         <v>0</v>
       </c>
       <c r="CJ41">
-        <f>+raw!AB41</f>
+        <f>+raw!AD41</f>
         <v>0</v>
       </c>
       <c r="CL41">
-        <f>+raw!AC41</f>
+        <f>+raw!AE41</f>
         <v>0</v>
       </c>
       <c r="CN41">
-        <f>+raw!AD41</f>
+        <f>+raw!AF41</f>
         <v>0</v>
       </c>
       <c r="CP41">
-        <f>+raw!AE41</f>
+        <f>+raw!AG41</f>
         <v>0</v>
       </c>
     </row>
@@ -17155,111 +17239,111 @@
         <v>0</v>
       </c>
       <c r="AQ42">
-        <f>+raw!E42</f>
+        <f>+raw!F42</f>
         <v>0</v>
       </c>
       <c r="AS42">
-        <f>+raw!F42</f>
+        <f>+raw!H42</f>
         <v>0</v>
       </c>
       <c r="AU42">
-        <f>+raw!G42</f>
+        <f>+raw!I42</f>
         <v>0</v>
       </c>
       <c r="AW42">
-        <f>+raw!H42</f>
+        <f>+raw!J42</f>
         <v>0</v>
       </c>
       <c r="AY42">
-        <f>+raw!I42</f>
+        <f>+raw!K42</f>
         <v>0</v>
       </c>
       <c r="BA42">
-        <f>+raw!J42</f>
+        <f>+raw!L42</f>
         <v>0</v>
       </c>
       <c r="BC42">
-        <f>+raw!K42</f>
+        <f>+raw!M42</f>
         <v>0</v>
       </c>
       <c r="BE42">
-        <f>+raw!L42</f>
+        <f>+raw!N42</f>
         <v>0</v>
       </c>
       <c r="BG42">
-        <f>+raw!M42</f>
+        <f>+raw!O42</f>
         <v>0</v>
       </c>
       <c r="BI42">
-        <f>+raw!N42</f>
+        <f>+raw!P42</f>
         <v>0</v>
       </c>
       <c r="BK42">
-        <f>+raw!O42</f>
+        <f>+raw!Q42</f>
         <v>0</v>
       </c>
       <c r="BM42">
-        <f>+raw!P42</f>
+        <f>+raw!R42</f>
         <v>0</v>
       </c>
       <c r="BO42">
-        <f>+raw!Q42</f>
+        <f>+raw!S42</f>
         <v>0</v>
       </c>
       <c r="BQ42">
-        <f>+raw!R42</f>
+        <f>+raw!T42</f>
         <v>0</v>
       </c>
       <c r="BS42">
-        <f>+raw!S42</f>
+        <f>+raw!U42</f>
         <v>0</v>
       </c>
       <c r="BU42">
-        <f>+raw!T42</f>
+        <f>+raw!V42</f>
         <v>0</v>
       </c>
       <c r="BW42">
-        <f>+raw!U42</f>
+        <f>+raw!W42</f>
         <v>0</v>
       </c>
       <c r="BY42">
-        <f>+raw!V42</f>
+        <f>+raw!X42</f>
         <v>0</v>
       </c>
       <c r="CA42">
-        <f>+raw!W42</f>
+        <f>+raw!Y42</f>
         <v>0</v>
       </c>
       <c r="CC42">
-        <f>+raw!X42</f>
+        <f>+raw!Z42</f>
         <v>0</v>
       </c>
       <c r="CE42">
-        <f>+raw!Y42</f>
+        <f>+raw!AA42</f>
         <v>0</v>
       </c>
       <c r="CG42">
-        <f>+raw!Z42</f>
+        <f>+raw!AB42</f>
         <v>0</v>
       </c>
       <c r="CI42">
-        <f>+raw!AA42</f>
+        <f>+raw!AC42</f>
         <v>0</v>
       </c>
       <c r="CK42">
-        <f>+raw!AB42</f>
+        <f>+raw!AD42</f>
         <v>0</v>
       </c>
       <c r="CM42">
-        <f>+raw!AC42</f>
+        <f>+raw!AE42</f>
         <v>0</v>
       </c>
       <c r="CO42">
-        <f>+raw!AD42</f>
+        <f>+raw!AF42</f>
         <v>0</v>
       </c>
       <c r="CQ42">
-        <f>+raw!AE42</f>
+        <f>+raw!AG42</f>
         <v>0</v>
       </c>
     </row>
@@ -19712,11 +19796,11 @@
       </c>
       <c r="BB54">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC54">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD54">
         <f t="shared" si="9"/>
@@ -19937,7 +20021,7 @@
       </c>
       <c r="BD55">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE55">
         <f t="shared" si="10"/>
